--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45426</v>
+        <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45167</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44630</v>
+        <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,46 +1674,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45372</v>
+        <v>46107</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,11 +1746,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1755,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1767,58 +1776,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1832,10 +1841,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,7 +1862,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1886,49 +1895,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1951,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46114</v>
+        <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,23 +1966,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1987,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1996,49 +2000,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,17 +2071,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2092,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2108,42 +2117,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2153,14 +2162,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45084</v>
+        <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2173,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2209,50 +2218,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2266,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>45167</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,26 +2290,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,42 +2331,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2380,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2397,7 +2401,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2433,39 +2437,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
@@ -2489,7 +2493,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2581,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2591,10 +2595,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,13 +2611,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2647,39 +2651,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45215</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>45792</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4130,11 +4130,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>45309</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4206,13 +4206,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4250,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4265,14 +4260,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44974</v>
+        <v>45884</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4285,7 +4280,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4328,7 +4323,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4342,10 +4337,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45169</v>
+        <v>44462</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4357,13 +4352,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4406,7 +4396,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4420,10 +4410,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44602</v>
+        <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4437,11 +4427,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4474,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4498,10 +4488,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44540</v>
+        <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4513,8 +4503,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4567,14 +4562,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4588,11 +4583,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4645,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45884</v>
+        <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4664,8 +4659,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45229</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,13 +4737,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4786,7 +4781,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4800,10 +4795,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4815,8 +4810,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45235</v>
+        <v>44834</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4890,11 +4890,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45607</v>
+        <v>45989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4966,13 +4966,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45044</v>
+        <v>44630</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5044,13 +5039,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5093,7 +5083,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5107,10 +5097,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44713</v>
+        <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5124,11 +5114,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5171,7 +5161,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5185,10 +5175,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44462</v>
+        <v>45173</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5201,7 +5191,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5244,7 +5234,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5258,10 +5248,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45989</v>
+        <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5274,7 +5264,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5317,7 +5307,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5331,10 +5321,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46132</v>
+        <v>46171</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5348,11 +5338,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5395,7 +5385,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5409,10 +5399,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46128</v>
+        <v>45874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5425,7 +5415,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>10.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5468,7 +5458,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5482,10 +5472,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45233</v>
+        <v>44974</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5497,13 +5487,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5546,7 +5531,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5556,14 +5541,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45275</v>
+        <v>46254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5575,13 +5560,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5624,7 +5604,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5634,14 +5614,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45121</v>
+        <v>45233</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5655,11 +5635,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5702,7 +5682,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5712,14 +5692,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45275</v>
+        <v>45235</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5737,7 +5717,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5797,7 +5777,7 @@
         <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5853,7 +5833,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5867,10 +5847,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46171</v>
+        <v>46227</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,13 +5862,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5931,7 +5906,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5945,10 +5920,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45274</v>
+        <v>46227</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5960,13 +5935,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6009,7 +5979,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6023,10 +5993,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45874</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6039,7 +6009,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.6</v>
+        <v>8.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6082,7 +6052,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6096,10 +6066,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45173</v>
+        <v>46227</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6112,7 +6082,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6155,7 +6125,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6169,10 +6139,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45054</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6184,8 +6154,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6228,7 +6203,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6242,10 +6217,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45243</v>
+        <v>46274</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,13 +6232,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6306,7 +6276,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6320,10 +6290,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45215</v>
+        <v>46274</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6336,7 +6306,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6379,7 +6349,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6393,10 +6363,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44730</v>
+        <v>46274</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6409,7 +6379,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6452,7 +6422,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6462,14 +6432,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6481,13 +6451,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6530,7 +6495,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6540,14 +6505,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44872</v>
+        <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6560,7 +6525,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6603,7 +6568,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6617,10 +6582,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44725</v>
+        <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6633,7 +6598,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6676,7 +6641,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6690,10 +6655,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6706,7 +6671,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6749,7 +6714,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6763,10 +6728,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45309</v>
+        <v>45274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6778,8 +6743,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6822,7 +6792,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6832,14 +6802,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44973</v>
+        <v>45050</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6851,8 +6821,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6895,7 +6870,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6909,10 +6884,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44841</v>
+        <v>45044</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6926,11 +6901,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6973,7 +6948,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6987,10 +6962,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46227</v>
+        <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7003,7 +6978,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7046,7 +7021,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7056,14 +7031,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44630</v>
+        <v>45275</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7075,8 +7050,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7119,7 +7099,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7133,10 +7113,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>45215</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7149,7 +7129,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7192,7 +7172,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7206,10 +7186,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46227</v>
+        <v>44730</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7222,7 +7202,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7265,7 +7245,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7279,10 +7259,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>44540</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7295,7 +7275,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7338,7 +7318,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7348,14 +7328,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7368,7 +7348,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7411,7 +7391,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7425,10 +7405,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>44713</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7440,8 +7420,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7484,7 +7469,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7498,10 +7483,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>45054</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7514,7 +7499,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7557,7 +7542,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7571,10 +7556,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7587,7 +7572,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7630,7 +7615,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7644,10 +7629,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46273</v>
+        <v>45607</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7659,8 +7644,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7703,7 +7693,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7713,14 +7703,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7732,8 +7722,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7786,14 +7781,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7805,8 +7800,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45309</v>
+        <v>44875</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7956,8 +7956,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8000,7 +8005,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8014,10 +8019,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45792</v>
+        <v>45309</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8029,13 +8034,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8095,7 +8095,7 @@
         <v>45791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45372</v>
+        <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45084</v>
+        <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,43 +1674,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
@@ -1734,7 +1730,7 @@
         <v>46107</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1840,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1933,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45989</v>
+        <v>45372</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,7 +1963,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1976,10 +1972,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1994,55 +1990,55 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2056,10 +2052,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46171</v>
+        <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,23 +2067,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2101,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2117,42 +2108,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,14 +2153,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45541</v>
+        <v>45084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2173,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,50 +2209,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2266,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45167</v>
+        <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2281,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2303,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2315,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2380,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2395,13 +2391,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2437,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44610</v>
+        <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,8 +2496,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2542,46 +2538,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2591,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,13 +2607,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2651,35 +2647,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44725</v>
+        <v>44834</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3607,8 +3607,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3651,7 +3656,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44610</v>
+        <v>45274</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3680,8 +3685,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3724,7 +3734,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3738,10 +3748,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44523</v>
+        <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3754,7 +3764,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3797,7 +3807,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3811,10 +3821,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44635</v>
+        <v>44610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3827,7 +3837,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3870,7 +3880,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3884,10 +3894,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44713</v>
+        <v>44523</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3899,13 +3909,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3953,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3967,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>44635</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3978,7 +3983,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45792</v>
+        <v>45173</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,13 +4055,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44841</v>
+        <v>44713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4130,11 +4130,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>10.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45309</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4206,8 +4206,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4250,7 +4255,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4260,14 +4265,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45884</v>
+        <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4280,7 +4285,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4323,7 +4328,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4333,14 +4338,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44462</v>
+        <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4352,8 +4357,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4396,7 +4406,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4410,10 +4420,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45229</v>
+        <v>45054</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4425,13 +4435,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4474,7 +4479,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44602</v>
+        <v>45243</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4552,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4562,14 +4567,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45121</v>
+        <v>44974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4581,13 +4586,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44910</v>
+        <v>45884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4659,13 +4659,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4703,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4717,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>45169</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,8 +4732,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4812,11 +4812,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44834</v>
+        <v>44540</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4888,13 +4888,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4937,7 +4932,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45989</v>
+        <v>44910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4966,8 +4961,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44630</v>
+        <v>45215</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45169</v>
+        <v>46132</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45173</v>
+        <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44725</v>
+        <v>45229</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5263,8 +5263,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5307,7 +5312,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5321,10 +5326,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46171</v>
+        <v>45229</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5336,13 +5341,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5385,7 +5385,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5399,10 +5399,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45874</v>
+        <v>45235</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5414,8 +5414,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>10.6</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5458,7 +5463,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5472,10 +5477,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44974</v>
+        <v>45607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5487,8 +5492,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5531,7 +5541,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5545,10 +5555,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46254</v>
+        <v>45044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5560,8 +5570,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5604,7 +5619,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5618,10 +5633,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45233</v>
+        <v>44730</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5633,13 +5648,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5682,7 +5692,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5696,10 +5706,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45235</v>
+        <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5713,11 +5723,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5760,7 +5770,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5774,10 +5784,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45756</v>
+        <v>45989</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5790,7 +5800,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5833,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5847,10 +5857,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46227</v>
+        <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5862,8 +5872,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5906,7 +5921,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5920,10 +5935,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46227</v>
+        <v>44462</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5936,7 +5951,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5979,7 +5994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5993,10 +6008,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46273</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6008,8 +6023,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6052,7 +6072,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6066,10 +6086,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46227</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6081,8 +6101,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6125,7 +6150,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6139,10 +6164,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45243</v>
+        <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6154,13 +6179,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6203,7 +6223,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6217,10 +6237,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6233,7 +6253,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6276,7 +6296,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6290,10 +6310,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46274</v>
+        <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6306,7 +6326,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6349,7 +6369,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6359,14 +6379,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6378,8 +6398,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6422,7 +6447,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6436,10 +6461,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46274</v>
+        <v>45121</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6451,8 +6476,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6495,7 +6525,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6505,14 +6535,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6525,7 +6555,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6568,7 +6598,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6582,10 +6612,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6598,7 +6628,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6641,7 +6671,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6651,14 +6681,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6670,8 +6700,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6714,7 +6749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6728,10 +6763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45274</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6743,13 +6778,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6792,7 +6822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6802,14 +6832,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45050</v>
+        <v>45756</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6821,13 +6851,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6870,7 +6895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6884,10 +6909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45044</v>
+        <v>44841</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6901,11 +6926,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6948,7 +6973,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6962,10 +6987,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45215</v>
+        <v>44630</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6978,7 +7003,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7021,7 +7046,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7031,14 +7056,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45275</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7050,13 +7075,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7099,7 +7119,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7113,10 +7133,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45215</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7129,7 +7149,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7172,7 +7192,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7186,10 +7206,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44730</v>
+        <v>46227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7202,7 +7222,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7245,7 +7265,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7259,10 +7279,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44540</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7275,7 +7295,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7318,7 +7338,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7328,14 +7348,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44973</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7348,7 +7368,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7391,7 +7411,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7405,10 +7425,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44713</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7420,13 +7440,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7469,7 +7484,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7483,10 +7498,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45054</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7499,7 +7514,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7542,7 +7557,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7556,10 +7571,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45229</v>
+        <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7572,7 +7587,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7615,7 +7630,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7629,10 +7644,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45607</v>
+        <v>46273</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7644,13 +7659,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7693,7 +7703,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7703,14 +7713,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7722,13 +7732,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7771,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7781,14 +7786,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45275</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7800,13 +7805,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44875</v>
+        <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7956,13 +7956,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8005,7 +8000,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8019,10 +8014,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45309</v>
+        <v>45792</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8034,8 +8029,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8095,7 +8095,7 @@
         <v>45791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45426</v>
+        <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45167</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44630</v>
+        <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,46 +1674,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1742,23 +1746,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1788,42 +1787,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,7 +1857,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1891,49 +1890,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1947,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45372</v>
+        <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1962,11 +1961,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1975,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1987,58 +1991,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,17 +2071,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2092,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2108,42 +2117,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2153,14 +2162,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45084</v>
+        <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2173,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2209,50 +2218,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2266,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46171</v>
+        <v>45167</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,26 +2290,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2323,46 +2327,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2380,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44610</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2391,8 +2395,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2428,46 +2437,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2490,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2496,13 +2505,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2538,46 +2542,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2591,10 +2595,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,13 +2611,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2647,39 +2651,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44834</v>
+        <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3607,13 +3607,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3656,7 +3651,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45274</v>
+        <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3685,13 +3680,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3734,7 +3724,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3748,10 +3738,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44725</v>
+        <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3764,7 +3754,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3807,7 +3797,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3821,10 +3811,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44610</v>
+        <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3837,7 +3827,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3880,7 +3870,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3894,10 +3884,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44523</v>
+        <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3909,8 +3899,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3953,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44635</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45173</v>
+        <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4055,8 +4050,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44713</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,13 +4128,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>10.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4187,14 +4182,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>45884</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4206,13 +4201,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4269,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45215</v>
+        <v>44462</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4285,7 +4275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4328,7 +4318,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4338,14 +4328,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45050</v>
+        <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4359,11 +4349,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4406,7 +4396,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4420,10 +4410,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45054</v>
+        <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4435,8 +4425,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4479,7 +4474,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4489,14 +4484,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45243</v>
+        <v>45121</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4510,11 +4505,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44974</v>
+        <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4586,8 +4581,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45884</v>
+        <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4659,8 +4659,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4703,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4717,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45169</v>
+        <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4732,13 +4737,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44602</v>
+        <v>44630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4810,13 +4810,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4854,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44540</v>
+        <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4888,8 +4883,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44910</v>
+        <v>45173</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4961,13 +4961,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5010,7 +5005,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45215</v>
+        <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5040,7 +5035,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5083,7 +5078,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5097,10 +5092,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5112,13 +5107,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5161,7 +5151,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5175,10 +5165,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46128</v>
+        <v>44974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5181,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5234,7 +5224,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5248,10 +5238,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45229</v>
+        <v>46132</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5265,11 +5255,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5312,7 +5302,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5326,10 +5316,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45229</v>
+        <v>45233</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5341,8 +5331,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5402,7 +5397,7 @@
         <v>45235</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5477,10 +5472,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45607</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5492,13 +5487,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5541,7 +5531,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5555,10 +5545,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45044</v>
+        <v>45243</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5572,11 +5562,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5619,7 +5609,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5633,10 +5623,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44730</v>
+        <v>45274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5648,8 +5638,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5692,7 +5687,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5702,14 +5697,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44713</v>
+        <v>45050</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5723,11 +5718,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5770,7 +5765,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5784,10 +5779,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45989</v>
+        <v>45044</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5799,8 +5794,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44602</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5872,13 +5872,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5921,7 +5916,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5931,14 +5926,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44462</v>
+        <v>45275</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5950,8 +5945,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5994,7 +5994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6023,13 +6023,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6072,7 +6067,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6086,10 +6081,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>44730</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6101,13 +6096,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6164,10 +6154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45874</v>
+        <v>44540</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6180,7 +6170,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.6</v>
+        <v>6.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6223,7 +6213,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6237,10 +6227,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44872</v>
+        <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6253,7 +6243,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6296,7 +6286,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6310,10 +6300,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44725</v>
+        <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6325,8 +6315,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6379,14 +6374,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45275</v>
+        <v>46171</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6404,7 +6399,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6447,7 +6442,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6457,14 +6452,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45121</v>
+        <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6476,13 +6471,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>10.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6525,7 +6515,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6539,10 +6529,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45309</v>
+        <v>45054</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6555,7 +6545,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6598,7 +6588,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6612,10 +6602,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44973</v>
+        <v>45229</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6628,7 +6618,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6671,7 +6661,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6681,14 +6671,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45275</v>
+        <v>45607</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6702,11 +6692,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6766,7 +6756,7 @@
         <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6822,7 +6812,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6836,10 +6826,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45756</v>
+        <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6851,8 +6841,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6895,7 +6890,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6905,14 +6900,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44841</v>
+        <v>45275</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6926,11 +6921,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44630</v>
+        <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7003,7 +6998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7046,7 +7041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7063,7 +7058,7 @@
         <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7076,7 +7071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7119,7 +7114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>46273</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7149,7 +7144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7192,7 +7187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7206,10 +7201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46227</v>
+        <v>45761</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7221,8 +7216,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7348,14 +7348,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7428,7 +7428,7 @@
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>44875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7513,8 +7513,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7557,7 +7562,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7574,7 +7579,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7587,7 +7592,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7630,7 +7635,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7640,14 +7645,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7660,7 +7665,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7720,7 +7725,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7776,7 +7781,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7793,7 +7798,7 @@
         <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7806,7 +7811,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7849,7 +7854,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7863,10 +7868,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45761</v>
+        <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7878,13 +7883,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 23284-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45372</v>
+        <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45084</v>
+        <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,50 +1674,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45989</v>
+        <v>45372</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1756,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1774,48 +1770,48 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
@@ -1839,7 +1835,7 @@
         <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1945,7 @@
         <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2038,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,14 +2048,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46171</v>
+        <v>45084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,13 +2067,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2117,42 +2108,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2161,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45541</v>
+        <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2181,8 +2176,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,50 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45167</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2286,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2303,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2315,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2331,42 +2332,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2380,10 +2381,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>45989</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2395,23 +2396,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2425,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2437,39 +2433,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2489,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2577,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2591,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,13 +2607,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2651,35 +2647,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>45215</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44841</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>44834</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,8 +4128,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4182,14 +4187,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45884</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4201,8 +4206,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4255,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4269,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44462</v>
+        <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4285,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4328,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4332,10 +4342,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45229</v>
+        <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4349,11 +4359,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4396,7 +4406,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4410,10 +4420,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44602</v>
+        <v>45169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4427,11 +4437,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4474,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4484,14 +4494,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45121</v>
+        <v>44540</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4503,13 +4513,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4569,7 +4574,7 @@
         <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4630,7 +4635,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4640,14 +4645,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44834</v>
+        <v>45884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4659,13 +4664,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45989</v>
+        <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,8 +4737,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4781,7 +4786,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44630</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4811,7 +4816,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4854,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45169</v>
+        <v>45235</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4885,11 +4890,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4932,7 +4937,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45173</v>
+        <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4961,8 +4966,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5019,10 +5029,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44725</v>
+        <v>45044</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5034,8 +5044,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5078,7 +5093,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5092,10 +5107,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46128</v>
+        <v>44713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5107,8 +5122,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5151,7 +5171,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5165,10 +5185,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44974</v>
+        <v>46132</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5180,8 +5200,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5224,7 +5249,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5238,10 +5263,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5253,13 +5278,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5302,7 +5322,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5316,10 +5336,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45233</v>
+        <v>44462</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5331,13 +5351,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5380,7 +5395,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5394,10 +5409,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45235</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5430,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5458,7 +5473,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5468,14 +5483,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5487,8 +5502,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5531,7 +5551,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5541,14 +5561,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45243</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5562,11 +5582,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5609,7 +5629,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5623,10 +5643,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45274</v>
+        <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5644,7 +5664,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5687,7 +5707,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5697,14 +5717,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45050</v>
+        <v>45874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5716,13 +5736,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5765,7 +5780,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5775,14 +5790,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45044</v>
+        <v>45275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5796,11 +5811,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5858,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5857,10 +5872,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45215</v>
+        <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5873,7 +5888,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5916,7 +5931,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5926,14 +5941,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5951,7 +5966,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5994,7 +6009,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6008,10 +6023,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6024,7 +6039,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6067,7 +6082,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6081,10 +6096,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44730</v>
+        <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6097,7 +6112,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6140,7 +6155,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,10 +6169,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44540</v>
+        <v>46254</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6170,7 +6185,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6213,7 +6228,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6227,10 +6242,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44973</v>
+        <v>45054</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6243,7 +6258,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6286,7 +6301,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6300,10 +6315,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44713</v>
+        <v>45243</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6317,11 +6332,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6364,7 +6379,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6378,10 +6393,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46171</v>
+        <v>46227</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6393,13 +6408,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6442,7 +6452,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6456,10 +6466,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45874</v>
+        <v>46227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6472,7 +6482,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6515,7 +6525,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6529,10 +6539,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45054</v>
+        <v>46227</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6545,7 +6555,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6588,7 +6598,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6602,10 +6612,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45229</v>
+        <v>45215</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6618,7 +6628,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6661,7 +6671,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6675,10 +6685,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45607</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6690,13 +6700,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6739,7 +6744,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6749,14 +6754,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6769,7 +6774,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6812,7 +6817,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6826,10 +6831,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6841,13 +6846,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45275</v>
+        <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6919,13 +6919,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6968,7 +6963,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6982,10 +6977,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6998,7 +6993,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7041,7 +7036,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7055,10 +7050,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7071,7 +7066,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7124,14 +7119,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7144,7 +7139,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.5</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7187,7 +7182,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7201,10 +7196,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45761</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7216,13 +7211,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7265,7 +7255,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7279,10 +7269,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46227</v>
+        <v>44730</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7295,7 +7285,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7338,7 +7328,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7352,10 +7342,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7367,8 +7357,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7411,7 +7406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7425,10 +7420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7441,7 +7436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7484,7 +7479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7498,10 +7493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44875</v>
+        <v>44725</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7513,13 +7508,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7562,7 +7552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7576,10 +7566,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7592,7 +7582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7635,7 +7625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7645,14 +7635,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7665,7 +7655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7708,7 +7698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7718,14 +7708,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>44841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7737,8 +7727,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7781,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7795,10 +7790,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>44630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7811,7 +7806,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7854,7 +7849,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46274</v>
+        <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7883,8 +7878,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 23284-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45426</v>
+        <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45167</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44630</v>
+        <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,46 +1674,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45372</v>
+        <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1743,7 +1747,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1752,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1770,55 +1774,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46107</v>
+        <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1849,11 +1853,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1893,42 +1897,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46114</v>
+        <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,13 +1961,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,49 +1995,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2048,14 +2051,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45084</v>
+        <v>45167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2068,20 +2071,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2092,10 +2095,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2104,50 +2107,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2161,10 +2160,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2181,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,46 +2217,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2270,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2286,13 +2285,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2328,46 +2322,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2381,10 +2375,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45989</v>
+        <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2396,17 +2390,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2421,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2437,42 +2436,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2486,10 +2485,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44610</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2501,8 +2500,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2535,49 +2539,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2591,10 +2595,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,13 +2611,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2647,39 +2651,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45215</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,13 +4050,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4094,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4108,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4130,11 +4125,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4191,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4208,11 +4203,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4250,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4269,10 +4264,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44974</v>
+        <v>44462</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4285,7 +4280,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4345,7 +4340,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4406,7 +4401,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4416,14 +4411,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45169</v>
+        <v>45121</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44540</v>
+        <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4513,8 +4508,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4588,11 +4588,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4652,7 +4652,7 @@
         <v>45884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45229</v>
+        <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,13 +4737,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4786,7 +4781,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4800,10 +4795,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4815,8 +4810,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45235</v>
+        <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4888,13 +4888,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4937,7 +4932,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45607</v>
+        <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4966,13 +4961,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5015,7 +5005,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5029,10 +5019,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45044</v>
+        <v>44974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5044,13 +5034,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5093,7 +5078,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5107,10 +5092,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44713</v>
+        <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5124,7 +5109,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -5171,7 +5156,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5185,10 +5170,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46132</v>
+        <v>45235</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5202,11 +5187,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5249,7 +5234,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5263,10 +5248,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5279,7 +5264,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5322,7 +5307,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5336,10 +5321,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44462</v>
+        <v>45989</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5352,7 +5337,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5395,7 +5380,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5409,10 +5394,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5430,7 +5415,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5473,7 +5458,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5483,14 +5468,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5508,7 +5493,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5551,7 +5536,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5565,10 +5550,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45121</v>
+        <v>45050</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5586,7 +5571,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5629,7 +5614,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5643,10 +5628,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46171</v>
+        <v>45044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5660,11 +5645,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5707,7 +5692,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5721,10 +5706,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45874</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5737,7 +5722,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5780,7 +5765,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5797,7 +5782,7 @@
         <v>45275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5815,7 +5800,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5858,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5872,10 +5857,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45756</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5888,7 +5873,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5931,7 +5916,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5945,10 +5930,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45274</v>
+        <v>44730</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5960,13 +5945,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6009,7 +5989,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6023,10 +6003,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45173</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,8 +6018,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6082,7 +6067,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6096,10 +6081,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45989</v>
+        <v>44540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6112,7 +6097,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6155,7 +6140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6169,10 +6154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46254</v>
+        <v>44973</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6185,7 +6170,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6228,7 +6213,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6242,10 +6227,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45054</v>
+        <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6257,8 +6242,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6301,7 +6291,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45243</v>
+        <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6330,13 +6320,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6379,7 +6364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6393,10 +6378,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46227</v>
+        <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6409,7 +6394,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6452,7 +6437,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6466,10 +6451,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46227</v>
+        <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6482,7 +6467,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6525,7 +6510,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6539,10 +6524,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46227</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6555,7 +6540,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6598,7 +6583,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6612,10 +6597,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45215</v>
+        <v>46132</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6627,8 +6612,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6671,7 +6661,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6685,10 +6675,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46274</v>
+        <v>45607</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6700,8 +6690,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6744,7 +6739,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6754,14 +6749,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46274</v>
+        <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6773,8 +6768,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6827,14 +6827,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6846,8 +6846,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6890,7 +6895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6904,10 +6909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6920,7 +6925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6963,7 +6968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6977,10 +6982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46274</v>
+        <v>45761</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6992,8 +6997,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7036,7 +7046,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7050,10 +7060,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>44875</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7065,8 +7075,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7109,7 +7124,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7119,14 +7134,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7139,7 +7154,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7182,7 +7197,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7196,10 +7211,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7212,7 +7227,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7255,7 +7270,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7269,10 +7284,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44730</v>
+        <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7285,7 +7300,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7328,7 +7343,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7342,10 +7357,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7357,13 +7372,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7406,7 +7416,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7420,10 +7430,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44872</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7436,7 +7446,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7479,7 +7489,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7493,10 +7503,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44725</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7509,7 +7519,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7552,7 +7562,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7566,10 +7576,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7582,7 +7592,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7625,7 +7635,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,14 +7645,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44973</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7655,7 +7665,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7698,7 +7708,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7708,14 +7718,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44841</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7727,13 +7737,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7781,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7790,10 +7795,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44630</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7806,7 +7811,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7849,7 +7854,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7863,10 +7868,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45761</v>
+        <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7878,13 +7883,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 23284-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>45167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>44610</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44462</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45121</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45235</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45989</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45274</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>45050</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>45044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>44730</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>44540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44973</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>46132</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45607</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45275</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>46254</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45761</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44875</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>46227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>46227</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46274</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45792</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45541</v>
+        <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1961,8 +1961,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>12.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1998,50 +2003,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2055,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45167</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2070,11 +2071,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2083,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2095,58 +2101,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2160,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44602</v>
+        <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2175,13 +2181,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2221,42 +2222,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44610</v>
+        <v>45167</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2286,20 +2291,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2310,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,46 +2327,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2375,10 +2380,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46107</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,11 +2397,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>12.9</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2432,46 +2437,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2485,10 +2490,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2500,13 +2505,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2539,42 +2539,42 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
         <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45309</v>
+        <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,8 +4050,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4094,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4108,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44841</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4123,13 +4128,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 51787-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45229</v>
+        <v>44462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4201,13 +4201,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4250,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4264,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44462</v>
+        <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4279,8 +4274,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45121</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44910</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44834</v>
+        <v>45884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4586,13 +4586,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4645,14 +4640,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45884</v>
+        <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4664,8 +4659,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44974</v>
+        <v>45989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45233</v>
+        <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5107,13 +5107,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5156,7 +5151,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5170,10 +5165,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45235</v>
+        <v>46171</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5186,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5248,10 +5243,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45756</v>
+        <v>45874</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5259,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>10.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5307,7 +5302,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45989</v>
+        <v>45233</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5336,8 +5331,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5380,7 +5380,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5394,10 +5394,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45243</v>
+        <v>45235</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5458,7 +5458,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45274</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5487,13 +5487,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5536,7 +5531,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5546,14 +5541,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45050</v>
+        <v>45243</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5567,11 +5562,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5614,7 +5609,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,10 +5623,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45044</v>
+        <v>45274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5645,11 +5640,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5692,7 +5687,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5702,14 +5697,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45215</v>
+        <v>45050</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5721,8 +5716,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45275</v>
+        <v>45044</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5796,11 +5796,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5860,7 +5860,7 @@
         <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5926,14 +5926,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44730</v>
+        <v>45275</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5945,8 +5945,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5989,7 +5994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6003,10 +6008,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46171</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6018,13 +6023,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44540</v>
+        <v>44730</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.7</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44973</v>
+        <v>44540</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>6.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44713</v>
+        <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6242,13 +6242,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6291,7 +6286,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6305,10 +6300,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45874</v>
+        <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6320,8 +6315,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45054</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45229</v>
+        <v>46132</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6466,8 +6466,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>46254</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6540,7 +6545,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6597,10 +6602,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46132</v>
+        <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6612,13 +6617,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45607</v>
+        <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6690,13 +6690,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6739,7 +6734,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6753,10 +6748,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44602</v>
+        <v>45607</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6770,11 +6765,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6817,7 +6812,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6827,14 +6822,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45275</v>
+        <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6846,13 +6841,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6895,7 +6885,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6909,10 +6899,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46254</v>
+        <v>46227</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6925,7 +6915,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6968,7 +6958,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6982,10 +6972,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45761</v>
+        <v>46273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6997,13 +6987,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7046,7 +7031,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7060,10 +7045,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44875</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7075,13 +7060,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7124,7 +7104,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7138,10 +7118,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7154,7 +7134,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7197,7 +7177,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7211,10 +7191,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7227,7 +7207,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7270,7 +7250,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7284,10 +7264,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7300,7 +7280,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7343,7 +7323,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7353,14 +7333,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7373,7 +7353,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7416,7 +7396,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7430,10 +7410,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7445,8 +7425,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7489,7 +7474,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7499,14 +7484,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7519,7 +7504,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7562,7 +7547,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7579,7 +7564,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7592,7 +7577,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7635,7 +7620,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7645,14 +7630,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7665,7 +7650,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7708,7 +7693,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7722,10 +7707,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7737,8 +7722,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7781,7 +7771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7795,10 +7785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>45761</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7810,8 +7800,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7854,7 +7849,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46274</v>
+        <v>44875</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7883,8 +7878,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45792</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE93"/>
+  <dimension ref="A1:AE92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45372</v>
+        <v>45791</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1427,11 +1427,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1440,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1452,51 +1457,51 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
@@ -1520,7 +1525,7 @@
         <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1630,7 @@
         <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1722,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1731,10 +1736,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45989</v>
+        <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1752,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1756,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1774,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,46 +1788,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1836,10 +1841,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46171</v>
+        <v>44630</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1851,19 +1856,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1893,46 +1893,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46107</v>
+        <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.9</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2003,46 +2003,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>45372</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,26 +2071,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2101,58 +2096,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2161,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45541</v>
+        <v>45989</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,17 +2177,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2206,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2218,50 +2213,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2266,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45167</v>
+        <v>46107</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2281,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2303,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2315,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2380,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2395,13 +2391,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2437,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44610</v>
+        <v>46114</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,8 +2496,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2539,49 +2535,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2591,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,13 +2607,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2651,42 +2647,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45791</v>
+        <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2717,11 +2717,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2761,35 +2761,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44610</v>
+        <v>44635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44523</v>
+        <v>44713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3753,8 +3753,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3797,7 +3802,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44635</v>
+        <v>45215</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3827,7 +3832,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3870,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3884,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44713</v>
+        <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3899,13 +3904,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>45050</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,8 +3977,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44841</v>
+        <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,13 +4055,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>44834</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,8 +4128,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51787-2021</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4191,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44462</v>
+        <v>45792</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4201,8 +4206,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4255,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 23284-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4269,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45229</v>
+        <v>45791</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4276,11 +4286,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4323,7 +4333,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4337,10 +4347,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44602</v>
+        <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4354,11 +4364,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4401,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4415,10 +4425,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45121</v>
+        <v>45884</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4430,13 +4440,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44910</v>
+        <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4510,11 +4515,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4567,14 +4572,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45884</v>
+        <v>44974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44834</v>
+        <v>45169</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4661,11 +4666,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44630</v>
+        <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,8 +4742,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4781,7 +4791,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4791,14 +4801,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45169</v>
+        <v>45275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4812,11 +4822,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45173</v>
+        <v>44540</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4889,7 +4899,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4932,7 +4942,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4942,14 +4952,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44725</v>
+        <v>45121</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4961,8 +4971,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5005,7 +5020,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5019,10 +5034,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45989</v>
+        <v>44910</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5034,8 +5049,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5078,7 +5098,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5088,14 +5108,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44974</v>
+        <v>45275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5107,8 +5127,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5151,7 +5176,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5165,10 +5190,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46171</v>
+        <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5182,11 +5207,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5229,7 +5254,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5243,10 +5268,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45874</v>
+        <v>45229</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5259,7 +5284,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.6</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5302,7 +5327,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5316,10 +5341,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45233</v>
+        <v>45235</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5362,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5380,7 +5405,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5394,10 +5419,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45235</v>
+        <v>45607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5411,7 +5436,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5475,7 +5500,7 @@
         <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5531,7 +5556,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5545,10 +5570,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45243</v>
+        <v>45044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5562,11 +5587,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5626,7 +5651,7 @@
         <v>45274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5687,7 +5712,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5697,14 +5722,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45050</v>
+        <v>44713</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5718,11 +5743,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5765,7 +5790,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5779,10 +5804,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45044</v>
+        <v>45989</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5794,13 +5819,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5863,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5857,10 +5877,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45215</v>
+        <v>45173</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5873,7 +5893,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5916,7 +5936,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5926,14 +5946,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45275</v>
+        <v>45054</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5945,13 +5965,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5994,7 +6009,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6008,10 +6023,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>45243</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6023,8 +6038,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6067,7 +6087,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6081,10 +6101,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44730</v>
+        <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6097,7 +6117,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6140,7 +6160,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,10 +6174,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44540</v>
+        <v>44730</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6170,7 +6190,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.7</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6213,7 +6233,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6227,10 +6247,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44973</v>
+        <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6242,8 +6262,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6286,7 +6311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6300,10 +6325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44713</v>
+        <v>44872</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6315,13 +6340,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6364,7 +6384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6378,10 +6398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6394,7 +6414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6454,7 +6474,7 @@
         <v>46132</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6515,7 +6535,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6529,10 +6549,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46254</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6545,7 +6565,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6588,7 +6608,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6602,10 +6622,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45054</v>
+        <v>45309</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6618,7 +6638,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6661,7 +6681,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6675,10 +6695,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45229</v>
+        <v>44973</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6691,7 +6711,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6734,7 +6754,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6748,10 +6768,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45607</v>
+        <v>44841</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6769,7 +6789,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6812,7 +6832,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6826,10 +6846,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46227</v>
+        <v>44630</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6842,7 +6862,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6885,7 +6905,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6899,10 +6919,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46227</v>
+        <v>45761</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6914,8 +6934,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6958,7 +6983,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6972,10 +6997,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46273</v>
+        <v>45309</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6988,7 +7013,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7031,7 +7056,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7045,10 +7070,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>46171</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7060,8 +7085,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7104,7 +7134,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7118,10 +7148,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46274</v>
+        <v>45874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7134,7 +7164,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7177,7 +7207,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7191,10 +7221,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7207,7 +7237,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7250,7 +7280,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7264,10 +7294,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7280,7 +7310,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7323,7 +7353,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7333,14 +7363,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7353,7 +7383,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7396,7 +7426,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7410,10 +7440,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7425,13 +7455,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7474,7 +7499,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7484,14 +7509,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7504,7 +7529,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7547,7 +7572,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7557,14 +7582,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7577,7 +7602,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7620,7 +7645,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7637,7 +7662,7 @@
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7650,7 +7675,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7693,7 +7718,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7703,14 +7728,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45275</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7722,13 +7747,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7771,7 +7791,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7785,10 +7805,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45761</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7800,13 +7820,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7849,7 +7864,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7863,10 +7878,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44875</v>
+        <v>46273</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7878,13 +7893,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7927,7 +7937,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7937,14 +7947,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7957,7 +7967,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8000,7 +8010,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8014,10 +8024,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45791</v>
+        <v>46274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8029,13 +8039,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8078,24 +8083,24 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>S 1582-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45792</v>
+        <v>45427</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8107,86 +8112,86 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S 710-2025</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>45720</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>S 1582-2024</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>45427</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8225,84 +8230,6 @@
         <v>0</v>
       </c>
       <c r="V92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>S 710-2025</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="n">
-        <v>45720</v>
-      </c>
-      <c r="E93" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45791</v>
+        <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1427,26 +1427,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1457,51 +1452,51 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
@@ -1525,7 +1520,7 @@
         <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1630,7 +1625,7 @@
         <v>45084</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1717,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1736,10 +1731,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45167</v>
+        <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1752,7 +1747,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1761,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1779,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1788,46 +1783,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1841,10 +1836,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44630</v>
+        <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1856,14 +1851,19 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1893,46 +1893,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44602</v>
+        <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>12.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2003,46 +2003,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45372</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,11 +2071,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2084,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2096,58 +2101,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2161,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45989</v>
+        <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2177,16 +2182,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2213,46 +2218,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2266,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46107</v>
+        <v>45167</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,26 +2290,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2323,46 +2327,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2380,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44610</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2391,8 +2395,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2428,46 +2437,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2490,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46114</v>
+        <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2496,13 +2505,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2535,49 +2539,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2591,10 +2595,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,13 +2611,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2647,46 +2651,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46171</v>
+        <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2717,11 +2717,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2761,35 +2761,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44635</v>
+        <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3724,7 +3724,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44713</v>
+        <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3753,13 +3753,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>10.1</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3797,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3816,10 +3811,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45215</v>
+        <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3832,7 +3827,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3875,7 +3870,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3884,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44610</v>
+        <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3904,8 +3899,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>10.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45050</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,13 +3977,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44523</v>
+        <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4055,8 +4050,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44834</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,13 +4128,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4191,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45792</v>
+        <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4208,11 +4203,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4250,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4265,14 +4260,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45791</v>
+        <v>45121</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4290,7 +4285,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4333,7 +4328,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4347,10 +4342,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44875</v>
+        <v>44910</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4364,11 +4359,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4421,14 +4416,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45884</v>
+        <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4440,8 +4435,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45233</v>
+        <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4513,13 +4513,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44974</v>
+        <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4591,8 +4586,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4635,7 +4635,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45169</v>
+        <v>44630</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4664,13 +4664,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4713,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44602</v>
+        <v>45169</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4744,11 +4739,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4791,7 +4786,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4801,14 +4796,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45275</v>
+        <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4820,13 +4815,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4883,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44540</v>
+        <v>44725</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4889,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4942,7 +4932,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4952,14 +4942,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45121</v>
+        <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4971,13 +4961,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5020,7 +5005,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5034,10 +5019,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44910</v>
+        <v>45989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5049,13 +5034,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5098,7 +5078,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5108,14 +5088,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45275</v>
+        <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5133,7 +5113,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5176,7 +5156,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5190,10 +5170,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45229</v>
+        <v>45235</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5207,11 +5187,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5254,7 +5234,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5268,10 +5248,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45229</v>
+        <v>45756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5284,7 +5264,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5327,7 +5307,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5341,10 +5321,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45235</v>
+        <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5362,7 +5342,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5405,7 +5385,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5419,10 +5399,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45607</v>
+        <v>45274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5436,11 +5416,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5483,7 +5463,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5493,14 +5473,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>45050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5512,8 +5492,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5573,7 +5558,7 @@
         <v>45044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5634,7 +5619,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5648,10 +5633,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45274</v>
+        <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5663,13 +5648,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5712,7 +5692,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5722,14 +5702,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44713</v>
+        <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5743,11 +5723,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5790,7 +5770,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5804,10 +5784,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,8 +5799,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5863,7 +5848,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5877,10 +5862,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45173</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5893,7 +5878,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5936,7 +5921,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5950,10 +5935,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45054</v>
+        <v>44730</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5966,7 +5951,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6009,7 +5994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6023,10 +6008,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45243</v>
+        <v>44540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6038,13 +6023,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6087,7 +6067,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6101,10 +6081,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45215</v>
+        <v>44973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6117,7 +6097,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6160,7 +6140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6174,10 +6154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44730</v>
+        <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6190,7 +6170,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>10.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6233,7 +6213,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6247,10 +6227,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44602</v>
+        <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6264,11 +6244,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6311,7 +6291,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6325,10 +6305,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44872</v>
+        <v>46128</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6341,7 +6321,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6384,7 +6364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6398,10 +6378,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44725</v>
+        <v>46132</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6413,8 +6393,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6457,7 +6442,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6471,10 +6456,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46132</v>
+        <v>45054</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6486,13 +6471,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6535,7 +6515,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6549,10 +6529,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6565,7 +6545,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6608,7 +6588,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6622,10 +6602,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45309</v>
+        <v>46254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6638,7 +6618,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6681,7 +6661,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 51813-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6695,10 +6675,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44973</v>
+        <v>45607</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6710,8 +6690,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6754,7 +6739,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6768,10 +6753,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44841</v>
+        <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6785,11 +6770,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6832,7 +6817,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6842,14 +6827,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44630</v>
+        <v>45275</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6861,8 +6846,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6905,7 +6895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6919,10 +6909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45761</v>
+        <v>46227</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6934,13 +6924,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6983,7 +6968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6997,10 +6982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45309</v>
+        <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7013,7 +6998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7056,7 +7041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7070,10 +7055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46171</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7085,13 +7070,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7134,7 +7114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7148,10 +7128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45874</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7164,7 +7144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>10.6</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7207,7 +7187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7221,10 +7201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7237,7 +7217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7280,7 +7260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7294,10 +7274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7310,7 +7290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7353,7 +7333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7367,10 +7347,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7383,7 +7363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7426,7 +7406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7436,14 +7416,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7456,7 +7436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7499,7 +7479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7509,14 +7489,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7529,7 +7509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7572,7 +7552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7582,14 +7562,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7602,7 +7582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7645,7 +7625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7662,7 +7642,7 @@
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7675,7 +7655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7718,7 +7698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 18222-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7732,10 +7712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>45761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7747,8 +7727,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7791,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7805,10 +7790,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>44875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7820,8 +7805,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7864,7 +7854,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7878,10 +7868,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46273</v>
+        <v>45309</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7894,7 +7884,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7937,7 +7927,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 23284-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7947,14 +7937,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46274</v>
+        <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7966,8 +7956,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8010,7 +8005,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8024,10 +8019,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46274</v>
+        <v>45792</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8039,8 +8034,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>45427</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45720</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE92"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45372</v>
+        <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1472,38 +1472,38 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1577,38 +1577,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1618,14 +1618,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45084</v>
+        <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1674,50 +1674,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45989</v>
+        <v>45372</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1756,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1774,55 +1770,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46171</v>
+        <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1853,11 +1849,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1897,42 +1893,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,7 +1963,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2000,49 +1996,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2056,10 +2052,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,23 +2067,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2101,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2110,49 +2101,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,14 +2153,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45541</v>
+        <v>45084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2173,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,50 +2209,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2266,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45167</v>
+        <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2281,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2303,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2315,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,39 +2323,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2383,7 +2379,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2489,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2581,7 +2577,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2591,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,13 +2607,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2651,35 +2647,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>44834</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,8 +3977,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44841</v>
+        <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,13 +4055,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4109,14 +4109,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,8 +4128,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4191,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45229</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4203,11 +4208,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4250,7 +4255,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4260,14 +4265,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45121</v>
+        <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4279,13 +4284,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44910</v>
+        <v>45169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4359,11 +4359,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
         <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44834</v>
+        <v>44540</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4586,13 +4586,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44630</v>
+        <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4664,8 +4659,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45169</v>
+        <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45173</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44725</v>
+        <v>45235</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4888,8 +4888,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4932,7 +4937,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44974</v>
+        <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4961,8 +4966,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5019,10 +5029,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45989</v>
+        <v>44713</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5034,8 +5044,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5078,7 +5093,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5092,10 +5107,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45233</v>
+        <v>46132</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5109,11 +5124,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5156,7 +5171,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5170,10 +5185,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45235</v>
+        <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5185,13 +5200,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5234,7 +5244,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5248,10 +5258,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45756</v>
+        <v>45989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5274,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5307,7 +5317,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5321,10 +5331,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45243</v>
+        <v>45233</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5342,7 +5352,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5385,7 +5395,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5399,10 +5409,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45274</v>
+        <v>46171</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5420,7 +5430,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5463,7 +5473,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5477,10 +5487,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45050</v>
+        <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5494,11 +5504,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5541,7 +5551,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5555,10 +5565,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45044</v>
+        <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5570,13 +5580,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>10.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5629,14 +5634,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45215</v>
+        <v>45121</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5648,8 +5653,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5692,7 +5702,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5709,7 +5719,7 @@
         <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5727,7 +5737,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46171</v>
+        <v>46254</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5799,13 +5809,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5848,7 +5853,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45215</v>
+        <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5878,7 +5883,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5921,7 +5926,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5935,10 +5940,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44730</v>
+        <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5950,8 +5955,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5994,7 +6004,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6008,10 +6018,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44540</v>
+        <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6024,7 +6034,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6067,7 +6077,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6081,10 +6091,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44973</v>
+        <v>46227</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6097,7 +6107,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6140,7 +6150,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,10 +6164,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45874</v>
+        <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6170,7 +6180,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.6</v>
+        <v>7.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6213,7 +6223,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6227,10 +6237,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44713</v>
+        <v>46227</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6242,13 +6252,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46128</v>
+        <v>46227</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6321,7 +6326,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46132</v>
+        <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6395,11 +6400,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6442,7 +6447,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6456,10 +6461,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45054</v>
+        <v>46274</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6472,7 +6477,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6515,7 +6520,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6525,14 +6530,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45229</v>
+        <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6545,7 +6550,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6588,7 +6593,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6602,10 +6607,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6618,7 +6623,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6661,7 +6666,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51813-2024</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45607</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6690,13 +6695,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6768,13 +6768,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6817,7 +6812,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6827,14 +6822,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45275</v>
+        <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6846,13 +6841,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6895,7 +6885,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6905,14 +6895,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6925,7 +6915,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6968,7 +6958,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6982,10 +6972,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6998,7 +6988,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7041,7 +7031,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7055,10 +7045,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>45215</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7071,7 +7061,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7114,7 +7104,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7128,10 +7118,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>44730</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7144,7 +7134,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7187,7 +7177,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7201,10 +7191,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7216,8 +7206,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7260,7 +7255,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7274,10 +7269,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7290,7 +7285,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7333,7 +7328,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>44725</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7363,7 +7358,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7406,7 +7401,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7416,14 +7411,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7436,7 +7431,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7479,7 +7474,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7489,14 +7484,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7509,7 +7504,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7552,7 +7547,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7566,10 +7561,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7581,8 +7576,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46274</v>
+        <v>44630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18222-2025</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45761</v>
+        <v>45309</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7727,13 +7727,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7790,10 +7785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44875</v>
+        <v>45792</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7807,7 +7802,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7854,24 +7849,24 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>S 1582-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45309</v>
+        <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7884,7 +7879,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7924,27 +7919,27 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="15" customHeight="1">
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23284-2025</t>
+          <t>S 710-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45791</v>
+        <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7962,7 +7957,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8001,235 +7996,6 @@
         <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>A 23655-2025</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>45792</v>
-      </c>
-      <c r="E90" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>S 1582-2024</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>45427</v>
-      </c>
-      <c r="E91" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>S 710-2025</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>45720</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45372</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44834</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44540</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45235</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44713</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>46132</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45233</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>46171</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45121</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46254</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>46227</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46227</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>46227</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46274</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45215</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44730</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44872</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44725</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45309</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45792</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45372</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46114</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44834</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44540</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45235</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44713</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>46132</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45233</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>46171</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45121</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46254</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>46227</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46227</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>46227</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46274</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45215</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44730</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44872</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44725</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45309</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45792</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45426</v>
+        <v>45791</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1427,11 +1427,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1440,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1452,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,46 +1469,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1522,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45167</v>
+        <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1566,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1577,38 +1582,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1622,10 +1627,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44630</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1638,20 +1643,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1662,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,42 +1683,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1723,14 +1728,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45372</v>
+        <v>45084</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1743,10 +1748,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1755,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1767,58 +1772,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1832,10 +1841,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1847,23 +1856,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1893,42 +1897,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1946,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1963,7 +1967,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1996,49 +2000,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,10 +2056,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45989</v>
+        <v>46114</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,17 +2071,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2092,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2101,49 +2110,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2153,14 +2162,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45084</v>
+        <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,8 +2181,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2213,46 +2227,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2266,10 +2276,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46171</v>
+        <v>45541</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,13 +2291,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2323,46 +2328,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2385,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>45167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2391,26 +2400,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2421,10 +2425,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2437,42 +2441,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2486,10 +2490,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44610</v>
+        <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2501,8 +2505,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2538,46 +2547,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2591,10 +2600,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,7 +2616,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2643,50 +2652,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2705,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45791</v>
+        <v>44630</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,19 +2720,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2757,39 +2757,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44834</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,13 +3977,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45215</v>
+        <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4051,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4094,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4109,14 +4104,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45050</v>
+        <v>45792</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4134,7 +4129,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4187,14 +4182,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>45884</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4206,13 +4201,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4269,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44974</v>
+        <v>44841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4284,8 +4274,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4328,7 +4323,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4342,10 +4337,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45169</v>
+        <v>45309</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4357,13 +4352,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4406,7 +4396,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4420,10 +4410,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44602</v>
+        <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4437,11 +4427,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4484,7 +4474,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4494,14 +4484,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45884</v>
+        <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4513,8 +4503,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4567,14 +4562,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44540</v>
+        <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4586,8 +4581,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45229</v>
+        <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,13 +4737,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4786,7 +4781,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4800,10 +4795,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>44834</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4815,8 +4810,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45235</v>
+        <v>44630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4888,13 +4888,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4937,7 +4932,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45044</v>
+        <v>45169</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4968,11 +4963,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44713</v>
+        <v>45173</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5044,13 +5039,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5093,7 +5083,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5107,10 +5097,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46132</v>
+        <v>44725</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5122,13 +5112,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5188,7 +5173,7 @@
         <v>46128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5244,7 +5229,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5258,10 +5243,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45989</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5274,7 +5259,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5317,7 +5302,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5331,10 +5316,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45233</v>
+        <v>46132</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5348,11 +5333,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5395,7 +5380,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5409,10 +5394,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46171</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5430,7 +5415,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5473,7 +5458,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5483,14 +5468,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45275</v>
+        <v>45235</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5508,7 +5493,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5551,7 +5536,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5565,10 +5550,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45874</v>
+        <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5581,7 +5566,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10.6</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5624,7 +5609,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5634,14 +5619,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45121</v>
+        <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5655,11 +5640,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5702,7 +5687,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5712,14 +5697,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5737,7 +5722,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5780,7 +5765,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5790,14 +5775,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46254</v>
+        <v>45050</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,8 +5794,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5853,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5867,10 +5857,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45756</v>
+        <v>45044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5882,8 +5872,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5926,7 +5921,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5940,10 +5935,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45274</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5955,13 +5950,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6004,7 +5994,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6014,14 +6004,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45173</v>
+        <v>45275</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6033,8 +6023,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6077,7 +6072,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46227</v>
+        <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6107,7 +6102,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6150,7 +6145,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6164,10 +6159,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45054</v>
+        <v>44730</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6180,7 +6175,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46227</v>
+        <v>44540</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6253,7 +6248,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46227</v>
+        <v>44973</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6326,7 +6321,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45243</v>
+        <v>44713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6400,11 +6395,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6447,7 +6442,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6461,10 +6456,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46274</v>
+        <v>46171</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6476,8 +6471,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6530,14 +6530,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46274</v>
+        <v>45874</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46274</v>
+        <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46274</v>
+        <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46273</v>
+        <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6841,8 +6841,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6885,7 +6890,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6899,10 +6904,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6914,8 +6919,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6958,7 +6968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6972,10 +6982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6988,7 +6998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7031,7 +7041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7045,10 +7055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45215</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7104,7 +7114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7118,10 +7128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44730</v>
+        <v>46273</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7134,7 +7144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7177,7 +7187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7206,13 +7216,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7255,7 +7260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7269,10 +7274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44872</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7285,7 +7290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7328,7 +7333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7342,10 +7347,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44725</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7358,7 +7363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7401,7 +7406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7415,10 +7420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7431,7 +7436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7474,7 +7479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7484,14 +7489,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44973</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7504,7 +7509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7547,7 +7552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7557,14 +7562,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44841</v>
+        <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7576,13 +7581,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44630</v>
+        <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7654,8 +7654,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7698,7 +7703,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7712,10 +7717,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7728,7 +7733,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7771,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7785,10 +7790,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45792</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7800,13 +7805,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45791</v>
+        <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1427,26 +1427,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1457,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1469,46 +1464,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1522,10 +1517,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45372</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,11 +1532,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1562,58 +1562,58 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>45167</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1687,38 +1687,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1728,14 +1728,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45084</v>
+        <v>44630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1784,50 +1784,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1841,10 +1837,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45989</v>
+        <v>45372</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1853,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1866,10 +1862,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1884,55 +1880,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1946,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1961,23 +1957,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1991,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2007,42 +1998,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2056,10 +2047,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2077,7 +2068,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2110,49 +2101,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2157,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46171</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2183,11 +2174,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2220,49 +2211,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2272,14 +2263,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45541</v>
+        <v>45084</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2292,7 +2283,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2328,50 +2319,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2385,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45167</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2400,11 +2391,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2413,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2425,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2441,42 +2437,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,10 +2486,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44602</v>
+        <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2511,7 +2507,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2547,39 +2543,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2603,7 +2599,7 @@
         <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2691,7 +2687,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2705,10 +2701,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2721,13 +2717,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2761,35 +2757,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>44834</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,8 +3977,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45309</v>
+        <v>44875</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,8 +4055,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4094,7 +4104,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4108,10 +4118,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45792</v>
+        <v>45215</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4123,13 +4133,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4177,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4191,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45884</v>
+        <v>45050</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4201,8 +4206,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4255,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4269,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44841</v>
+        <v>45792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4280,7 +4290,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4323,7 +4333,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4337,10 +4347,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45309</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4353,7 +4363,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4396,7 +4406,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4406,14 +4416,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45229</v>
+        <v>45884</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4425,13 +4435,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4474,7 +4479,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44602</v>
+        <v>45169</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4505,11 +4510,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4562,14 +4567,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45121</v>
+        <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4583,11 +4588,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44910</v>
+        <v>44540</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4659,13 +4664,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>6.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45989</v>
+        <v>44910</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4737,8 +4737,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4781,7 +4786,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44834</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4812,11 +4817,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4859,7 +4864,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4873,10 +4878,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44630</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4889,7 +4894,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4932,7 +4937,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45169</v>
+        <v>45235</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4963,11 +4968,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5010,7 +5015,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5024,10 +5029,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45173</v>
+        <v>45044</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5039,8 +5044,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5083,7 +5093,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5097,10 +5107,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44725</v>
+        <v>44713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5112,8 +5122,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5156,7 +5171,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5170,10 +5185,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46128</v>
+        <v>45989</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5186,7 +5201,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5229,7 +5244,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5243,10 +5258,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44974</v>
+        <v>45233</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5258,8 +5273,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5319,7 +5339,7 @@
         <v>46132</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5380,7 +5400,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5394,10 +5414,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>46128</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5409,13 +5429,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5458,7 +5473,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5468,14 +5483,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45235</v>
+        <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5493,7 +5508,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5536,7 +5551,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5546,14 +5561,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45756</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5565,8 +5580,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5609,7 +5629,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5619,14 +5639,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45243</v>
+        <v>45275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5644,7 +5664,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5687,7 +5707,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5701,10 +5721,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45274</v>
+        <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5716,13 +5736,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5765,7 +5780,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5775,14 +5790,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45050</v>
+        <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5796,11 +5811,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5858,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5857,10 +5872,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45044</v>
+        <v>46171</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5874,11 +5889,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5921,7 +5936,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5935,10 +5950,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>45173</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5951,7 +5966,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5994,7 +6009,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6004,14 +6019,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45275</v>
+        <v>45874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6023,13 +6038,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>10.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6072,7 +6082,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6086,10 +6096,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45215</v>
+        <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6102,7 +6112,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6145,7 +6155,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6159,10 +6169,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44730</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6174,8 +6184,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6218,7 +6233,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6232,10 +6247,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44540</v>
+        <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6248,7 +6263,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6291,7 +6306,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6305,10 +6320,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44973</v>
+        <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6321,7 +6336,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6364,7 +6379,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6378,10 +6393,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44713</v>
+        <v>44602</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6395,11 +6410,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6442,7 +6457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6456,10 +6471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46171</v>
+        <v>46254</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6471,13 +6486,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6520,7 +6530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6534,10 +6544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45874</v>
+        <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6550,7 +6560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>10.6</v>
+        <v>4.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6593,7 +6603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6607,10 +6617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45054</v>
+        <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6623,7 +6633,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6666,7 +6676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6680,10 +6690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45229</v>
+        <v>45309</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6696,7 +6706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6739,7 +6749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6753,10 +6763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>44973</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6769,7 +6779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6812,7 +6822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6826,10 +6836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6841,13 +6851,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6890,7 +6895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6900,14 +6905,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45275</v>
+        <v>46227</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6919,13 +6924,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6985,7 +6985,7 @@
         <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7124,14 +7124,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7260,7 +7260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7277,7 +7277,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7350,7 +7350,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7479,7 +7479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7496,7 +7496,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7562,14 +7562,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44875</v>
+        <v>44841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7656,11 +7656,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>44630</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46041</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44862</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1408,14 +1408,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45426</v>
+        <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1452,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,46 +1464,50 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1517,10 +1521,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>44630</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1532,19 +1536,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1574,46 +1573,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1627,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45167</v>
+        <v>45541</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1643,10 +1642,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1655,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1667,10 +1666,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1683,42 +1682,46 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44630</v>
+        <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1748,20 +1751,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1772,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1788,42 +1791,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1837,10 +1840,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45372</v>
+        <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1852,11 +1855,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1865,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1877,58 +1885,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1950,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45989</v>
+        <v>44610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1966,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,42 +2006,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2047,10 +2055,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46107</v>
+        <v>45791</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2068,7 +2076,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>12.9</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2108,42 +2116,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2157,10 +2165,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>45372</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,26 +2180,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2202,58 +2205,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2263,14 +2266,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45084</v>
+        <v>45426</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,20 +2286,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2307,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2319,50 +2322,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2375,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>45989</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2391,23 +2390,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2421,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2433,46 +2427,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2486,10 +2480,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46171</v>
+        <v>46107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2503,11 +2497,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2547,42 +2541,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2596,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44610</v>
+        <v>46114</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,8 +2605,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2645,49 +2644,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2701,10 +2700,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45541</v>
+        <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2716,8 +2715,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2753,43 +2757,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19608-2022</t>
+          <t>A 73212-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44693</v>
+        <v>44550</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3310,8 +3310,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3354,7 +3359,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24656-2022</t>
+          <t>A 19608-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3368,10 +3373,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44726</v>
+        <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3384,7 +3389,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3444,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3500,7 +3505,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 73212-2021</t>
+          <t>A 24656-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3514,10 +3519,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44550</v>
+        <v>44726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,13 +3534,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44725</v>
+        <v>44523</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44610</v>
+        <v>44713</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3680,8 +3680,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>10.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3724,7 +3729,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3738,10 +3743,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44523</v>
+        <v>44725</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3754,7 +3759,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3797,7 +3802,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44635</v>
+        <v>44610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3827,7 +3832,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3870,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3884,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44713</v>
+        <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3899,13 +3904,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44834</v>
+        <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3979,11 +3979,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44875</v>
+        <v>45274</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4114,14 +4114,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45215</v>
+        <v>45121</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4133,8 +4133,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4177,7 +4182,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4187,14 +4192,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45050</v>
+        <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4208,11 +4213,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4255,7 +4260,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4269,10 +4274,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45792</v>
+        <v>44872</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4284,13 +4289,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4343,14 +4343,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>45275</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4362,8 +4362,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45884</v>
+        <v>45050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4435,8 +4440,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4479,7 +4489,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4493,10 +4503,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45169</v>
+        <v>45044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4510,11 +4520,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4557,7 +4567,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,10 +4581,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44602</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4586,13 +4596,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4635,7 +4640,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4645,14 +4650,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44540</v>
+        <v>45275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4664,8 +4669,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4708,7 +4718,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4722,10 +4732,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44910</v>
+        <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4739,11 +4749,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>45215</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4815,13 +4825,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4864,7 +4869,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4878,10 +4883,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>44730</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4894,7 +4899,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4937,7 +4942,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4951,10 +4956,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45235</v>
+        <v>44540</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4966,13 +4971,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45044</v>
+        <v>44973</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5044,13 +5044,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5093,7 +5088,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5107,10 +5102,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44713</v>
+        <v>44875</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5128,7 +5123,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5171,7 +5166,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5185,10 +5180,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45989</v>
+        <v>44713</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5200,8 +5195,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45233</v>
+        <v>44630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5273,13 +5273,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5322,7 +5317,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5336,10 +5331,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46132</v>
+        <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5351,13 +5346,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5400,7 +5390,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5414,10 +5404,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46128</v>
+        <v>45169</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5429,8 +5419,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5473,7 +5468,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5483,14 +5478,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45275</v>
+        <v>45173</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5502,13 +5497,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5551,7 +5541,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5561,14 +5551,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45121</v>
+        <v>45792</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5586,7 +5576,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5629,7 +5619,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5639,14 +5629,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45275</v>
+        <v>44841</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5660,11 +5650,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45756</v>
+        <v>45309</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5737,7 +5727,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5780,7 +5770,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45274</v>
+        <v>44725</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5809,13 +5799,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5858,7 +5843,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5872,10 +5857,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46171</v>
+        <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5887,13 +5872,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5936,7 +5916,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5950,10 +5930,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45173</v>
+        <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5966,7 +5946,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6009,7 +5989,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6023,10 +6003,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45874</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6039,7 +6019,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.6</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6082,7 +6062,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6096,10 +6076,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45054</v>
+        <v>45233</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,8 +6091,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6155,7 +6140,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6169,10 +6154,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45243</v>
+        <v>45235</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6190,7 +6175,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6233,7 +6218,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6247,10 +6232,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45215</v>
+        <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6262,8 +6247,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6306,7 +6296,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6320,10 +6310,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44730</v>
+        <v>45756</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6336,7 +6326,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6379,7 +6369,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6393,10 +6383,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44602</v>
+        <v>45243</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6414,7 +6404,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6457,7 +6447,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6471,10 +6461,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46254</v>
+        <v>44602</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6486,8 +6476,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6530,7 +6525,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6540,14 +6535,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44872</v>
+        <v>45884</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6560,7 +6555,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6603,7 +6598,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6617,10 +6612,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44725</v>
+        <v>45989</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6633,7 +6628,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45309</v>
+        <v>46128</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44973</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6778,8 +6773,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46227</v>
+        <v>46171</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6851,8 +6851,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46227</v>
+        <v>45874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46227</v>
+        <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6998,7 +7003,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7041,7 +7046,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7055,10 +7060,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7071,7 +7076,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7114,7 +7119,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7124,14 +7129,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7144,7 +7149,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7187,7 +7192,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7201,10 +7206,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7217,7 +7222,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7260,7 +7265,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7290,7 +7295,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7333,7 +7338,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7350,7 +7355,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7363,7 +7368,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7406,7 +7411,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7420,10 +7425,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7436,7 +7441,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7479,7 +7484,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7489,14 +7494,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7509,7 +7514,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7552,7 +7557,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7562,14 +7567,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7582,7 +7587,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7625,7 +7630,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7635,14 +7640,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44841</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7654,13 +7659,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44630</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3294-2026</t>
+          <t>A 40842-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46041</v>
+        <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -878,46 +878,165 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Rynkskinn
+Ullticka
+Björksplintborre
+Vågbandad barkbock
+Spillkråka
+Timmerticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 40842-2026 artfynd.xlsx", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 40842-2026 karta.png", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 40842-2026 georefererad karta.tif", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 40842-2026 FSC-klagomål.docx", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 40842-2026 FSC-klagomål mail.docx", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 40842-2026 tillsynsbegäran.docx", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 40842-2026 tillsynsbegäran mail.docx", "A 40842-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 40842-2026 prioriterade fågelarter.docx", "A 40842-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 3294-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>19</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Motaggsvamp
@@ -926,111 +1045,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 3294-2026 artfynd.xlsx", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 3294-2026 karta.png", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 3294-2026 georefererad karta.tif", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 3294-2026 FSC-klagomål.docx", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 3294-2026 FSC-klagomål mail.docx", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 3294-2026 tillsynsbegäran.docx", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 3294-2026 tillsynsbegäran mail.docx", "A 3294-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 3294-2026 prioriterade fågelarter.docx", "A 3294-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 37039-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Igelkott
@@ -1038,476 +1157,367 @@
 Svart trolldruva</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37039-2026 artfynd.xlsx", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37039-2026 karta.png", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37039-2026 georefererad karta.tif", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37039-2026 FSC-klagomål.docx", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37039-2026 FSC-klagomål mail.docx", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37039-2026 tillsynsbegäran.docx", "A 37039-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37039-2026 tillsynsbegäran mail.docx", "A 37039-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 49680-2022</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>44862</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>2.4</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Granbarkgnagare</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 49680-2022 artfynd.xlsx", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 49680-2022 karta.png", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 49680-2022 georefererad karta.tif", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 49680-2022 FSC-klagomål.docx", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 49680-2022 FSC-klagomål mail.docx", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 49680-2022 tillsynsbegäran.docx", "A 49680-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 49680-2022 tillsynsbegäran mail.docx", "A 49680-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 19216-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>2.6</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallticka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 19216-2026 artfynd.xlsx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 19216-2026 karta.png", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 19216-2026 georefererad karta.tif", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 19216-2026 FSC-klagomål.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 19216-2026 FSC-klagomål mail.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 19216-2026 tillsynsbegäran.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 19216-2026 tillsynsbegäran mail.docx", "A 19216-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 37238-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>2.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Svart trolldruva</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37238-2026 artfynd.xlsx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37238-2026 karta.png", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37238-2026 georefererad karta.tif", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37238-2026 FSC-klagomål.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37238-2026 FSC-klagomål mail.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37238-2026 tillsynsbegäran.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37238-2026 tillsynsbegäran mail.docx", "A 37238-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 25754-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45084</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1521,10 +1531,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44630</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,20 +1547,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1561,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,42 +1587,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45541</v>
+        <v>45791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1641,8 +1651,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1678,43 +1693,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
@@ -1738,7 +1749,7 @@
         <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1837,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1840,10 +1851,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44602</v>
+        <v>44630</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1855,19 +1866,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1901,42 +1907,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1950,10 +1956,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44610</v>
+        <v>45372</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1966,20 +1972,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -1990,58 +1996,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2055,10 +2061,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45791</v>
+        <v>46107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,7 +2082,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2116,42 +2122,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 17009-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2165,10 +2171,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45372</v>
+        <v>46114</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2180,11 +2186,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2193,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2205,58 +2216,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2270,10 +2281,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45426</v>
+        <v>45989</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2286,7 +2297,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2295,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2313,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,46 +2333,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2371,14 +2382,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45989</v>
+        <v>45084</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2391,16 +2402,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2415,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2431,42 +2442,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2480,10 +2495,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46107</v>
+        <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,11 +2512,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>12.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2541,42 +2556,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,10 +2605,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46114</v>
+        <v>44602</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,11 +2622,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2644,49 +2659,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2715,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46171</v>
+        <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,13 +2730,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2761,59 +2771,59 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S 1552-2023</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45055</v>
+        <v>45541</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2823,21 +2833,16 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2864,49 +2869,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S 1147-2023</t>
+          <t>S 1552-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2920,10 +2929,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45020</v>
+        <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2937,20 +2946,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2965,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2974,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S 495-2026</t>
+          <t>S 1147-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3030,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46073</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,23 +3056,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3078,76 +3087,72 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12578-2022</t>
+          <t>S 495-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44638</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,11 +3164,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3172,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3184,26 +3194,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 74173-2021</t>
+          <t>A 12578-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3217,10 +3263,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44558</v>
+        <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,13 +3278,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3281,7 +3322,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 73212-2021</t>
+          <t>A 74173-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3295,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44550</v>
+        <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3316,7 +3357,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3376,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3432,7 +3473,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44531-2022</t>
+          <t>A 24656-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3446,10 +3487,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44840</v>
+        <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3462,7 +3503,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3505,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24656-2022</t>
+          <t>A 44531-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3519,10 +3560,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44726</v>
+        <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3535,7 +3576,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3578,7 +3619,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 73212-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3592,10 +3633,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44523</v>
+        <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3607,8 +3648,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3651,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3665,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44713</v>
+        <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3680,13 +3726,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>10.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3729,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3743,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44725</v>
+        <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3759,7 +3800,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3843,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3816,10 +3857,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44610</v>
+        <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3832,7 +3873,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3892,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3948,7 +3989,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +4003,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44602</v>
+        <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3979,11 +4020,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45274</v>
+        <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4055,13 +4096,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4104,7 +4140,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4118,10 +4154,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45121</v>
+        <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4139,7 +4175,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4182,7 +4218,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4196,10 +4232,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44910</v>
+        <v>44834</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4213,11 +4249,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4260,7 +4296,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4274,10 +4310,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44872</v>
+        <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4289,8 +4325,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4333,7 +4374,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4343,14 +4384,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45275</v>
+        <v>45792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4364,11 +4405,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4411,7 +4452,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4421,14 +4462,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45050</v>
+        <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4440,13 +4481,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4489,7 +4525,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4499,14 +4535,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45044</v>
+        <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4518,13 +4554,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4567,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4581,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45215</v>
+        <v>45169</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4596,8 +4627,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4640,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4650,14 +4686,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45275</v>
+        <v>44602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4675,7 +4711,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4718,7 +4754,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4732,10 +4768,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44834</v>
+        <v>44540</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4747,13 +4783,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4796,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4810,10 +4841,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45215</v>
+        <v>44910</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4825,8 +4856,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4869,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4883,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44730</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4898,8 +4934,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4942,7 +4983,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4956,10 +4997,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44540</v>
+        <v>45229</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +5013,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5015,7 +5056,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5029,10 +5070,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44973</v>
+        <v>45235</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5044,8 +5085,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5088,7 +5134,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5102,10 +5148,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44875</v>
+        <v>45044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5119,11 +5165,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5166,7 +5212,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5180,10 +5226,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44713</v>
+        <v>46132</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5197,11 +5243,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5244,7 +5290,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5258,10 +5304,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44630</v>
+        <v>46128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5317,7 +5363,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5331,10 +5377,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45309</v>
+        <v>44713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5346,8 +5392,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5390,7 +5441,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5404,10 +5455,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45169</v>
+        <v>45989</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5419,13 +5470,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5468,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5482,10 +5528,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45173</v>
+        <v>45233</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5497,8 +5543,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5541,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5551,14 +5602,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5572,11 +5623,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5619,7 +5670,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5629,14 +5680,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44841</v>
+        <v>45121</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5654,7 +5705,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5697,7 +5748,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5711,10 +5762,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45309</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5726,8 +5777,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5770,7 +5826,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5784,10 +5840,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44725</v>
+        <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5800,7 +5856,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5843,7 +5899,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5853,14 +5909,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45054</v>
+        <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5872,8 +5928,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5916,7 +5977,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5930,10 +5991,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45229</v>
+        <v>45756</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5946,7 +6007,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5989,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6003,10 +6064,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>45274</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6018,8 +6079,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6062,7 +6128,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6076,10 +6142,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45233</v>
+        <v>45173</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6091,13 +6157,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6140,7 +6201,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6154,10 +6215,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45235</v>
+        <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6169,13 +6230,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6218,7 +6274,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6232,10 +6288,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45229</v>
+        <v>45243</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6249,11 +6305,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6296,7 +6352,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6310,10 +6366,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45756</v>
+        <v>46227</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6326,7 +6382,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6369,7 +6425,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6383,10 +6439,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45243</v>
+        <v>46227</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6398,13 +6454,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6447,7 +6498,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6461,10 +6512,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6476,13 +6527,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6525,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6535,14 +6581,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45884</v>
+        <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6555,7 +6601,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6598,7 +6644,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6608,14 +6654,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45989</v>
+        <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6628,7 +6674,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6671,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6685,10 +6731,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46128</v>
+        <v>45215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6701,7 +6747,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6744,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6758,10 +6804,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46132</v>
+        <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6773,13 +6819,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6822,7 +6863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6836,10 +6877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46171</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6851,13 +6892,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6900,7 +6936,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6914,10 +6950,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45874</v>
+        <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6930,7 +6966,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6973,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6987,10 +7023,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46254</v>
+        <v>46273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7003,7 +7039,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7046,7 +7082,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7056,14 +7092,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7076,7 +7112,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7119,7 +7155,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7133,10 +7169,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7149,7 +7185,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7192,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7206,10 +7242,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46273</v>
+        <v>44730</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7222,7 +7258,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7265,7 +7301,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7279,10 +7315,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46227</v>
+        <v>44602</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7294,8 +7330,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7338,7 +7379,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7352,10 +7393,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7368,7 +7409,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7411,7 +7452,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7425,10 +7466,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>44725</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7441,7 +7482,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7484,7 +7525,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7498,10 +7539,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7514,7 +7555,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7557,7 +7598,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7567,14 +7608,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7587,7 +7628,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7630,7 +7671,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7640,14 +7681,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7660,7 +7701,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7703,7 +7744,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7717,10 +7758,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>44841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7732,8 +7773,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7776,7 +7822,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7790,10 +7836,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>44630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7806,7 +7852,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7849,153 +7895,226 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
+          <t>A 2177-2024</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>45309</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>S 1582-2024</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D89" s="1" t="n">
         <v>45427</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
+      <c r="E89" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>0.2</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>S 710-2025</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D89" s="1" t="n">
+      <c r="D90" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="E90" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="I90" t="n">
         <v>0.3</v>
       </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE90"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1546,11 +1546,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1559,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1571,10 +1576,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1583,46 +1588,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1636,10 +1641,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45791</v>
+        <v>45372</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1651,26 +1656,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1681,58 +1681,58 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45167</v>
+        <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1806,38 +1806,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44630</v>
+        <v>45084</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1903,46 +1903,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1956,10 +1960,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45372</v>
+        <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1971,11 +1975,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1984,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1996,58 +2005,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2061,10 +2070,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,23 +2085,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2106,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2122,42 +2126,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17009-2026</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46114</v>
+        <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,11 +2192,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2225,49 +2229,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 17009-2026 artfynd.xlsx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 17009-2026 karta.png", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 17009-2026 georefererad karta.tif", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 17009-2026 FSC-klagomål.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 17009-2026 FSC-klagomål mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 17009-2026 tillsynsbegäran.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 17009-2026 tillsynsbegäran mail.docx", "A 17009-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2281,10 +2285,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45989</v>
+        <v>45541</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2297,16 +2301,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2321,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2333,46 +2337,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2382,14 +2390,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45084</v>
+        <v>45167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2402,20 +2410,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2426,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2438,50 +2446,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2495,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,7 +2520,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2552,46 +2556,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2605,10 +2609,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2620,13 +2624,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2662,46 +2661,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2715,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44610</v>
+        <v>44630</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2731,13 +2730,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2767,63 +2766,63 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>S 1552-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45541</v>
+        <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,16 +2832,21 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1.3</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2869,53 +2873,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S 1552-2023</t>
+          <t>S 1147-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45055</v>
+        <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S 1147-2023</t>
+          <t>S 495-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45020</v>
+        <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,23 +3056,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3087,72 +3087,76 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S 495-2026</t>
+          <t>A 12578-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46073</v>
+        <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,16 +3168,11 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3182,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3194,62 +3193,26 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
-        <v/>
-      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12578-2022</t>
+          <t>A 74173-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3263,10 +3226,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44638</v>
+        <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3278,8 +3241,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3322,7 +3290,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 74173-2021</t>
+          <t>A 19608-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3304,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44558</v>
+        <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3351,13 +3319,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3400,7 +3363,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19608-2022</t>
+          <t>A 24656-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3414,10 +3377,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44693</v>
+        <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3430,7 +3393,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3473,7 +3436,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24656-2022</t>
+          <t>A 44531-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3487,10 +3450,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44726</v>
+        <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3503,7 +3466,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3546,7 +3509,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44531-2022</t>
+          <t>A 73212-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3560,10 +3523,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44840</v>
+        <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3575,8 +3538,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3619,7 +3587,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 73212-2021</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3633,10 +3601,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44550</v>
+        <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3648,13 +3616,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3697,7 +3660,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3711,10 +3674,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44725</v>
+        <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3727,7 +3690,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3770,7 +3733,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3784,10 +3747,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44610</v>
+        <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3800,7 +3763,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3843,7 +3806,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3857,10 +3820,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44523</v>
+        <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3873,7 +3836,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3916,7 +3879,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3930,10 +3893,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44635</v>
+        <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3945,8 +3908,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>10.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3989,7 +3957,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4003,10 +3971,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44713</v>
+        <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4018,13 +3986,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>10.1</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4067,7 +4030,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4081,10 +4044,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45215</v>
+        <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4097,7 +4060,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4140,7 +4103,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4154,10 +4117,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45050</v>
+        <v>45884</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,13 +4132,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4218,7 +4176,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4232,10 +4190,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4249,11 +4207,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4296,7 +4254,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4310,10 +4268,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44875</v>
+        <v>45309</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4325,13 +4283,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4391,7 +4344,7 @@
         <v>45792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4452,7 +4405,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4466,10 +4419,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44974</v>
+        <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4481,8 +4434,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4525,7 +4483,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4535,14 +4493,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45884</v>
+        <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4554,8 +4512,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4561,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4608,14 +4571,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45169</v>
+        <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4633,7 +4596,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4639,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4653,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44602</v>
+        <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4707,11 +4670,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4754,7 +4717,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4768,10 +4731,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44540</v>
+        <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4784,7 +4747,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4827,7 +4790,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4841,10 +4804,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44910</v>
+        <v>44834</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4858,11 +4821,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4905,7 +4868,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4919,10 +4882,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4934,13 +4897,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4983,7 +4941,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4997,10 +4955,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45229</v>
+        <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5012,8 +4970,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5056,7 +5019,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5070,10 +5033,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45235</v>
+        <v>44630</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5085,13 +5048,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5134,7 +5092,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5148,10 +5106,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45044</v>
+        <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5165,11 +5123,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5212,7 +5170,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5226,10 +5184,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46132</v>
+        <v>45173</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5241,13 +5199,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5290,7 +5243,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5304,10 +5257,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46128</v>
+        <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5320,7 +5273,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5363,7 +5316,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5377,10 +5330,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44713</v>
+        <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5392,13 +5345,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5441,7 +5389,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5455,10 +5403,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45989</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5470,8 +5418,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5514,7 +5467,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5528,10 +5481,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45233</v>
+        <v>45235</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5549,7 +5502,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5592,7 +5545,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5602,14 +5555,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45275</v>
+        <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5621,13 +5574,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5670,7 +5618,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5680,14 +5628,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45121</v>
+        <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,11 +5649,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5748,7 +5696,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5762,10 +5710,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5783,7 +5731,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5843,7 +5791,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5899,7 +5847,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5909,14 +5857,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5934,7 +5882,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5977,7 +5925,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5987,14 +5935,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45756</v>
+        <v>45050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6006,8 +5954,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6050,7 +6003,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6064,10 +6017,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45274</v>
+        <v>45044</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6081,11 +6034,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6128,7 +6081,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6142,10 +6095,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45173</v>
+        <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6158,7 +6111,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6201,7 +6154,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6211,14 +6164,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45054</v>
+        <v>45275</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6230,8 +6183,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6274,7 +6232,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6288,10 +6246,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45243</v>
+        <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6303,13 +6261,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6352,7 +6305,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6366,10 +6319,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46227</v>
+        <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6382,7 +6335,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6425,7 +6378,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6439,10 +6392,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46227</v>
+        <v>44540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6455,7 +6408,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6498,7 +6451,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6512,10 +6465,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46227</v>
+        <v>44973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6528,7 +6481,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6571,7 +6524,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6585,10 +6538,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46274</v>
+        <v>44713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6600,8 +6553,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6644,7 +6602,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6654,14 +6612,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6674,7 +6632,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6717,7 +6675,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6731,10 +6689,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45215</v>
+        <v>46227</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6747,7 +6705,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6790,7 +6748,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,10 +6762,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6820,7 +6778,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6863,7 +6821,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6877,10 +6835,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6893,7 +6851,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6936,7 +6894,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6953,7 +6911,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6966,7 +6924,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +6967,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +6981,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,7 +6997,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7082,7 +7040,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7092,14 +7050,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7112,7 +7070,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7155,7 +7113,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7165,14 +7123,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7185,7 +7143,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7186,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7238,14 +7196,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44730</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7258,7 +7216,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7301,7 +7259,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,10 +7273,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7330,13 +7288,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7379,7 +7332,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7393,10 +7346,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44872</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7409,7 +7362,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7452,7 +7405,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7466,10 +7419,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44725</v>
+        <v>45054</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7482,7 +7435,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7525,7 +7478,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7539,10 +7492,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45309</v>
+        <v>45229</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7555,7 +7508,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7598,7 +7551,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7612,10 +7565,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44973</v>
+        <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7627,8 +7580,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7688,7 +7646,7 @@
         <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7744,7 +7702,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7754,14 +7712,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44841</v>
+        <v>45275</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7775,11 +7733,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7822,7 +7780,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7836,10 +7794,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44630</v>
+        <v>44875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7851,8 +7809,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7895,24 +7858,24 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>S 1582-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45309</v>
+        <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7925,7 +7888,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7965,10 +7928,10 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="15" customHeight="1">
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 1582-2024</t>
+          <t>S 710-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7982,10 +7945,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45427</v>
+        <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7997,8 +7960,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8037,84 +8005,6 @@
         <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>S 710-2025</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>45720</v>
-      </c>
-      <c r="E90" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45372</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45084</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45541</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44630</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45884</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>45309</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>45792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44834</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44630</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45173</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45235</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45274</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>45044</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45275</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46227</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46227</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>46273</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>45054</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45229</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45275</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45372</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45084</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>46171</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45541</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44630</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>44638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>44558</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44693</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44550</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>44872</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45884</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>45309</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>45792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45229</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45121</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44834</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>46128</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44630</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45173</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45235</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>46171</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45274</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>45044</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45275</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44973</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46227</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46227</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>46273</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>45054</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45229</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45275</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1546,26 +1546,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1576,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1588,46 +1583,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1641,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45372</v>
+        <v>45167</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1657,7 +1652,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1690,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1701,38 +1696,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,10 +1741,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45426</v>
+        <v>44630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1762,19 +1757,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1786,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1802,42 +1797,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1847,14 +1842,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45084</v>
+        <v>45372</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1867,20 +1862,20 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -1891,55 +1886,51 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
@@ -1963,7 +1954,7 @@
         <v>46107</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2064,7 @@
         <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2161,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2171,14 +2162,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46171</v>
+        <v>45084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2190,13 +2181,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2236,42 +2222,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2285,10 +2275,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45541</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,8 +2290,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2341,46 +2336,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2394,10 +2385,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45167</v>
+        <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2409,11 +2400,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2422,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2434,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2446,46 +2442,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2495,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44602</v>
+        <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2514,13 +2510,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2556,46 +2547,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2609,10 +2600,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44610</v>
+        <v>45541</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2625,7 +2616,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2661,46 +2652,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44630</v>
+        <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2729,14 +2724,19 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2766,63 +2766,63 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S 1552-2023</t>
+          <t>A 41251-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45055</v>
+        <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2836,17 +2836,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2873,49 +2873,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S 1147-2023</t>
+          <t>S 1552-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45020</v>
+        <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,20 +2946,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1552-2023 artfynd.xlsx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1552-2023 karta.png", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1552-2023 georefererad karta.tif", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1552-2023 FSC-klagomål.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1552-2023 FSC-klagomål mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1552-2023 tillsynsbegäran.docx", "S 1552-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1552-2023 tillsynsbegäran mail.docx", "S 1552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S 495-2026</t>
+          <t>S 1147-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46073</v>
+        <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,23 +3056,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3087,76 +3087,72 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 1147-2023 artfynd.xlsx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 1147-2023 karta.png", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 1147-2023 georefererad karta.tif", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 1147-2023 FSC-klagomål.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 1147-2023 FSC-klagomål mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 1147-2023 tillsynsbegäran.docx", "S 1147-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 1147-2023 tillsynsbegäran mail.docx", "S 1147-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12578-2022</t>
+          <t>S 495-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44638</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3168,11 +3164,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3181,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3193,26 +3194,62 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/S 495-2026 artfynd.xlsx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/S 495-2026 karta.png", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/S 495-2026 georefererad karta.tif", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/knärot/S 495-2026 karta knärot.png", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/S 495-2026 FSC-klagomål.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/S 495-2026 FSC-klagomål mail.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/S 495-2026 tillsynsbegäran.docx", "S 495-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/S 495-2026 tillsynsbegäran mail.docx", "S 495-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 74173-2021</t>
+          <t>A 12578-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3226,10 +3263,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44558</v>
+        <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3241,13 +3278,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3290,7 +3322,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19608-2022</t>
+          <t>A 74173-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3304,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44693</v>
+        <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3319,8 +3351,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3363,7 +3400,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24656-2022</t>
+          <t>A 19608-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3377,10 +3414,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44726</v>
+        <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3393,7 +3430,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3436,7 +3473,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44531-2022</t>
+          <t>A 24656-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3450,10 +3487,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44840</v>
+        <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3466,7 +3503,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3509,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 73212-2021</t>
+          <t>A 44531-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3523,10 +3560,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44550</v>
+        <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3538,13 +3575,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3587,7 +3619,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 73212-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3601,10 +3633,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44725</v>
+        <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3616,8 +3648,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3660,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3674,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44610</v>
+        <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3690,7 +3727,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3733,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3747,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44523</v>
+        <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3763,7 +3800,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3806,7 +3843,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3820,10 +3857,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44635</v>
+        <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3836,7 +3873,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3879,7 +3916,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3893,10 +3930,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44713</v>
+        <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3908,13 +3945,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.1</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3957,7 +3989,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3971,10 +4003,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44872</v>
+        <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3986,8 +4018,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>10.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4030,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4044,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45309</v>
+        <v>45215</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4060,7 +4097,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4103,7 +4140,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4117,10 +4154,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45884</v>
+        <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4132,8 +4169,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4176,7 +4218,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4190,10 +4232,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44841</v>
+        <v>44834</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4207,11 +4249,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4254,7 +4296,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4268,10 +4310,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45309</v>
+        <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4283,8 +4325,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4327,7 +4374,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4341,10 +4388,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45792</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4356,13 +4403,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4405,7 +4447,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4419,10 +4461,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45229</v>
+        <v>45169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4436,11 +4478,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4500,7 +4542,7 @@
         <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4561,7 +4603,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4571,14 +4613,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45121</v>
+        <v>44540</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4590,13 +4632,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4656,7 +4693,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4717,7 +4754,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4727,14 +4764,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45989</v>
+        <v>45884</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4747,7 +4784,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4790,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4804,10 +4841,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44834</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4821,11 +4858,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4868,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4882,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46128</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4898,7 +4935,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4941,7 +4978,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4955,10 +4992,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46132</v>
+        <v>45235</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,11 +5009,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5019,7 +5056,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5033,10 +5070,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44630</v>
+        <v>45044</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5048,8 +5085,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5092,7 +5134,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5106,10 +5148,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45169</v>
+        <v>44713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5123,11 +5165,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5170,7 +5212,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5184,10 +5226,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45173</v>
+        <v>46132</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5199,8 +5241,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5243,7 +5290,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5257,10 +5304,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44725</v>
+        <v>45989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5273,7 +5320,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5316,7 +5363,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5330,10 +5377,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44974</v>
+        <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5346,7 +5393,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5406,7 +5453,7 @@
         <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5467,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5477,14 +5524,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45235</v>
+        <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5502,7 +5549,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5545,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5555,14 +5602,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45756</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5574,8 +5621,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5618,7 +5670,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5628,14 +5680,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46171</v>
+        <v>45275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5653,7 +5705,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5696,7 +5748,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5710,10 +5762,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45243</v>
+        <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5731,7 +5783,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5774,7 +5826,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5788,10 +5840,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45874</v>
+        <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5804,7 +5856,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.6</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5847,7 +5899,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5861,10 +5913,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45274</v>
+        <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5876,13 +5928,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>10.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5925,7 +5972,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5935,14 +5982,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45050</v>
+        <v>45274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5956,11 +6003,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6003,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6017,10 +6064,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45044</v>
+        <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6032,13 +6079,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6081,7 +6123,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6095,10 +6137,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45215</v>
+        <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6111,7 +6153,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6154,7 +6196,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6164,14 +6206,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45275</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6189,7 +6231,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6232,7 +6274,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6249,7 +6291,7 @@
         <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6262,7 +6304,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6322,7 +6364,7 @@
         <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6378,7 +6420,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6392,10 +6434,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44540</v>
+        <v>44602</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6407,8 +6449,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6451,7 +6498,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6465,10 +6512,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44973</v>
+        <v>46227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6481,7 +6528,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6524,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6538,10 +6585,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44713</v>
+        <v>46227</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6553,13 +6600,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6602,7 +6644,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6619,7 +6661,7 @@
         <v>46227</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6632,7 +6674,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6675,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6689,10 +6731,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6705,7 +6747,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6748,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6758,14 +6800,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6778,7 +6820,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6821,7 +6863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6835,10 +6877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6851,7 +6893,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6894,7 +6936,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6911,7 +6953,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6924,7 +6966,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6967,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6984,7 +7026,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6997,7 +7039,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7040,7 +7082,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7054,10 +7096,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7070,7 +7112,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7113,7 +7155,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7130,7 +7172,7 @@
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7143,7 +7185,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7186,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7196,14 +7238,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7216,7 +7258,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7259,7 +7301,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7273,10 +7315,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7289,7 +7331,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7332,7 +7374,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7346,10 +7388,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>44725</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7362,7 +7404,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7405,7 +7447,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7419,10 +7461,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45054</v>
+        <v>45309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7435,7 +7477,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7478,7 +7520,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7492,10 +7534,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45229</v>
+        <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7508,7 +7550,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7551,7 +7593,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7565,10 +7607,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44602</v>
+        <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7582,11 +7624,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7629,7 +7671,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7643,10 +7685,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46254</v>
+        <v>44630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7659,7 +7701,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7702,7 +7744,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7712,14 +7754,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45275</v>
+        <v>45309</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7731,13 +7773,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7780,7 +7817,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7794,10 +7831,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44875</v>
+        <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7809,13 +7846,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7858,153 +7890,231 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
+          <t>A 23655-2025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>S 1582-2024</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D89" s="1" t="n">
         <v>45427</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
+      <c r="E89" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>0.2</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>S 710-2025</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D89" s="1" t="n">
+      <c r="D90" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="E90" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="I90" t="n">
         <v>0.3</v>
       </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45426</v>
+        <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1591,38 +1591,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45167</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1696,38 +1696,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44630</v>
+        <v>45084</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1793,46 +1793,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1846,10 +1850,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45372</v>
+        <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,11 +1865,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1874,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,58 +1895,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1951,10 +1960,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1966,23 +1975,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1996,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2012,42 +2016,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2061,10 +2065,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45989</v>
+        <v>46171</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2076,17 +2080,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2101,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2117,42 +2126,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,14 +2171,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45084</v>
+        <v>45541</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2191,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,50 +2227,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2275,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>45167</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,26 +2299,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2320,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,42 +2340,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2385,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,7 +2410,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2442,39 +2446,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
@@ -2498,7 +2502,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2586,7 +2590,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 41251-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2600,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45541</v>
+        <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,8 +2619,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2652,50 +2661,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45791</v>
+        <v>44630</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2724,19 +2729,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2766,46 +2766,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41251-2026</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46300</v>
+        <v>45791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2884,31 +2884,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45215</v>
+        <v>44872</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4150,14 +4150,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45050</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,13 +4169,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4218,7 +4213,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4232,10 +4227,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4249,11 +4244,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4296,7 +4291,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4306,14 +4301,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44875</v>
+        <v>45884</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4325,13 +4320,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4374,7 +4364,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4388,10 +4378,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4403,8 +4393,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4447,7 +4442,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4461,10 +4456,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45169</v>
+        <v>44602</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4478,11 +4473,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4525,7 +4520,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4535,14 +4530,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44602</v>
+        <v>45121</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4556,11 +4551,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4603,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4617,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44540</v>
+        <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4632,8 +4627,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44910</v>
+        <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4707,11 +4707,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45884</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4858,11 +4858,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>44630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45235</v>
+        <v>45989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5007,13 +5007,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5056,7 +5051,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45044</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5087,11 +5082,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5134,7 +5129,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5148,10 +5143,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44713</v>
+        <v>45874</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5163,13 +5158,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5212,7 +5202,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5226,10 +5216,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46132</v>
+        <v>45169</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5247,7 +5237,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5290,7 +5280,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5304,10 +5294,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45989</v>
+        <v>45173</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5320,7 +5310,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5363,7 +5353,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5377,10 +5367,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46128</v>
+        <v>44725</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5393,7 +5383,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5436,7 +5426,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5450,10 +5440,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45233</v>
+        <v>44974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5465,13 +5455,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5514,7 +5499,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5524,14 +5509,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45275</v>
+        <v>45233</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5549,7 +5534,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5592,7 +5577,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5602,14 +5587,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45121</v>
+        <v>45235</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5623,11 +5608,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5670,7 +5655,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5680,14 +5665,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45275</v>
+        <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5699,13 +5684,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5748,7 +5728,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5762,10 +5742,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46171</v>
+        <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5783,7 +5763,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5826,7 +5806,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5840,10 +5820,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45756</v>
+        <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5855,8 +5835,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5899,7 +5884,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5909,14 +5894,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45874</v>
+        <v>45050</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5928,8 +5913,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>10.6</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5972,7 +5962,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5986,10 +5976,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45274</v>
+        <v>45044</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6003,11 +5993,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45173</v>
+        <v>45215</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45054</v>
+        <v>46227</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45243</v>
+        <v>46227</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6225,13 +6215,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6274,7 +6259,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6288,10 +6273,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45215</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6304,7 +6289,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6347,7 +6332,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6357,14 +6342,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44730</v>
+        <v>45275</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6376,8 +6361,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6420,7 +6410,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6434,10 +6424,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6449,13 +6439,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6498,7 +6483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6512,10 +6497,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6528,7 +6513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6571,7 +6556,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6585,10 +6570,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6601,7 +6586,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6644,7 +6629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6658,10 +6643,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6674,7 +6659,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6717,7 +6702,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6727,14 +6712,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6747,7 +6732,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6790,7 +6775,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6807,7 +6792,7 @@
         <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6820,7 +6805,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6863,7 +6848,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6880,7 +6865,7 @@
         <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6893,7 +6878,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6936,7 +6921,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6953,7 +6938,7 @@
         <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6966,7 +6951,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +6994,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +7008,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46274</v>
+        <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,7 +7024,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7082,7 +7067,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7096,10 +7081,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>44730</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7112,7 +7097,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7155,7 +7140,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7165,14 +7150,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46274</v>
+        <v>44540</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7185,7 +7170,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7213,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7242,10 +7227,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7258,7 +7243,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7301,7 +7286,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,10 +7300,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44872</v>
+        <v>44713</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7330,8 +7315,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7374,7 +7364,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7388,10 +7378,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44725</v>
+        <v>45054</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7404,7 +7394,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7447,7 +7437,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7461,10 +7451,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45309</v>
+        <v>45229</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7477,7 +7467,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7520,7 +7510,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7534,10 +7524,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44973</v>
+        <v>46254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7550,7 +7540,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7593,7 +7583,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7607,10 +7597,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44841</v>
+        <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7624,11 +7614,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7671,7 +7661,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7681,14 +7671,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44630</v>
+        <v>45275</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7700,8 +7690,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7744,7 +7739,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7758,10 +7753,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45309</v>
+        <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7773,8 +7768,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46254</v>
+        <v>45309</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         <v>45792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45427</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45372</v>
+        <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1571,58 +1571,62 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1636,10 +1640,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>45791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1651,11 +1655,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1664,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1676,10 +1685,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1688,46 +1697,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1737,14 +1746,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45084</v>
+        <v>45426</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1757,20 +1766,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1781,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1793,50 +1802,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46107</v>
+        <v>45167</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1865,26 +1870,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1907,46 +1907,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45989</v>
+        <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1976,16 +1976,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2012,46 +2012,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2122,46 +2122,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45541</v>
+        <v>45372</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2191,20 +2191,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2215,62 +2215,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2280,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45167</v>
+        <v>45989</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,7 +2296,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2309,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2327,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,46 +2332,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2385,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2410,7 +2406,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2446,39 +2442,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2498,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2586,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41251-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2600,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46300</v>
+        <v>46107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2625,7 +2621,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>12.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2665,42 +2661,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2710,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44630</v>
+        <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,13 +2726,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2770,42 +2766,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 41251-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45791</v>
+        <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2884,31 +2884,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44725</v>
+        <v>44635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44610</v>
+        <v>44713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3799,8 +3799,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>10.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3843,7 +3848,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3857,10 +3862,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44523</v>
+        <v>44725</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3916,7 +3921,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3930,10 +3935,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44635</v>
+        <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3946,7 +3951,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3989,7 +3994,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4003,10 +4008,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44713</v>
+        <v>45215</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4018,13 +4023,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>10.1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44872</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,8 +4096,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4140,7 +4145,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4154,10 +4159,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>44523</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4170,7 +4175,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4213,7 +4218,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4227,10 +4232,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44841</v>
+        <v>44834</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4244,11 +4249,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4291,7 +4296,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4301,14 +4306,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45884</v>
+        <v>45309</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4321,7 +4326,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4364,7 +4369,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4374,14 +4379,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45229</v>
+        <v>45884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4393,13 +4398,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4442,7 +4442,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44602</v>
+        <v>44875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45121</v>
+        <v>45792</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>45233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4629,11 +4629,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44834</v>
+        <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4705,13 +4705,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4754,7 +4749,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>45169</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4783,8 +4778,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>45275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4858,11 +4858,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44630</v>
+        <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4934,8 +4934,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4978,7 +4983,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4988,14 +4993,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45989</v>
+        <v>45121</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5007,8 +5012,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5051,7 +5061,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46171</v>
+        <v>44540</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5080,13 +5090,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5129,7 +5134,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5143,10 +5148,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45874</v>
+        <v>44910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5158,8 +5163,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>10.6</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5202,7 +5212,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5212,14 +5222,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45169</v>
+        <v>45275</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5233,11 +5243,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5280,7 +5290,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5294,10 +5304,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45173</v>
+        <v>45229</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5309,8 +5319,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5353,7 +5368,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5367,10 +5382,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44725</v>
+        <v>45229</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5383,7 +5398,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5426,7 +5441,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5440,10 +5455,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44974</v>
+        <v>45235</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5455,8 +5470,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5499,7 +5519,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5513,10 +5533,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45233</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5528,13 +5548,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5577,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5591,10 +5606,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45235</v>
+        <v>45989</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5606,13 +5621,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5655,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5669,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45756</v>
+        <v>45044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5684,8 +5694,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5728,7 +5743,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5742,10 +5757,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45243</v>
+        <v>45274</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5763,7 +5778,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5806,7 +5821,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5820,10 +5835,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45274</v>
+        <v>44713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5837,11 +5852,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5884,7 +5899,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5894,14 +5909,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45050</v>
+        <v>45173</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5913,13 +5928,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5962,7 +5972,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5976,10 +5986,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45044</v>
+        <v>46171</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5993,11 +6003,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45215</v>
+        <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46227</v>
+        <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6142,8 +6152,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6186,7 +6201,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6200,10 +6215,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46227</v>
+        <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6216,7 +6231,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6259,7 +6274,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6273,10 +6288,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6289,7 +6304,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6332,7 +6347,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6342,14 +6357,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45275</v>
+        <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6361,13 +6376,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6420,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6434,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46227</v>
+        <v>44602</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6439,8 +6449,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6498,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6497,10 +6512,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46274</v>
+        <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6528,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,10 +6585,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46274</v>
+        <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6586,7 +6601,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6629,7 +6644,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6643,10 +6658,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46274</v>
+        <v>45309</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6659,7 +6674,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6702,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6712,14 +6727,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46274</v>
+        <v>44973</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6732,7 +6747,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6775,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 19217-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6785,14 +6800,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46274</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6804,8 +6819,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6848,7 +6868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6862,10 +6882,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46274</v>
+        <v>46128</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6878,7 +6898,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6921,7 +6941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6935,10 +6955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46274</v>
+        <v>44841</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6950,8 +6970,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6994,7 +7019,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7008,10 +7033,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45215</v>
+        <v>44630</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7024,7 +7049,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7067,7 +7092,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7081,10 +7106,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44730</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7097,7 +7122,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7140,7 +7165,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7154,10 +7179,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44540</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7170,7 +7195,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7213,7 +7238,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7227,10 +7252,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44973</v>
+        <v>46227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7243,7 +7268,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7286,7 +7311,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7300,10 +7325,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44713</v>
+        <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7315,13 +7340,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7364,7 +7384,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7374,14 +7394,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45054</v>
+        <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7394,7 +7414,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7437,7 +7457,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7451,10 +7471,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45229</v>
+        <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7467,7 +7487,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7510,7 +7530,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7524,10 +7544,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7540,7 +7560,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7583,7 +7603,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7597,10 +7617,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44602</v>
+        <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7612,13 +7632,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7661,7 +7676,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7671,14 +7686,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45275</v>
+        <v>46273</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7690,13 +7705,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7739,7 +7749,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7749,14 +7759,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44875</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7768,13 +7778,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7817,7 +7822,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7847,7 +7852,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7890,7 +7895,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7904,10 +7909,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45792</v>
+        <v>46254</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7919,13 +7924,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>45427</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE90"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45084</v>
+        <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,20 +1547,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1571,62 +1571,58 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1640,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45791</v>
+        <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1655,26 +1651,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1685,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1697,46 +1688,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,14 +1737,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45426</v>
+        <v>45084</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1766,10 +1757,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1778,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1790,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1802,46 +1793,50 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45167</v>
+        <v>46107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1870,11 +1865,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1907,46 +1907,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44630</v>
+        <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1976,17 +1976,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2012,46 +2012,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44602</v>
+        <v>45541</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,13 +2080,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,42 +2121,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2175,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45372</v>
+        <v>45167</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2191,7 +2190,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2224,10 +2223,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2235,38 +2234,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2280,10 +2279,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45989</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2295,17 +2294,22 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2320,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2332,39 +2336,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
@@ -2388,7 +2392,7 @@
         <v>46171</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2498,7 +2502,7 @@
         <v>44610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2586,7 +2590,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2600,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46107</v>
+        <v>44630</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,19 +2619,14 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>12.9</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2657,46 +2656,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2710,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45541</v>
+        <v>45791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2725,8 +2724,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2762,43 +2766,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11996-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44635</v>
+        <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44713</v>
+        <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3799,13 +3799,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>10.1</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3848,7 +3843,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3862,10 +3857,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44725</v>
+        <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3921,7 +3916,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 11996-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3935,10 +3930,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44610</v>
+        <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3951,7 +3946,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3994,7 +3989,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4008,10 +4003,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45215</v>
+        <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,8 +4018,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>44872</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,13 +4096,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4145,7 +4140,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4159,10 +4154,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44523</v>
+        <v>45309</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4175,7 +4170,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4218,7 +4213,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4232,10 +4227,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44834</v>
+        <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4249,11 +4244,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4296,7 +4291,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4310,10 +4305,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45309</v>
+        <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4325,8 +4320,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4379,14 +4379,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45884</v>
+        <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4398,8 +4398,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4442,7 +4447,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4452,14 +4457,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44875</v>
+        <v>45884</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4471,13 +4476,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45792</v>
+        <v>45121</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45233</v>
+        <v>44910</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4629,11 +4629,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44974</v>
+        <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4705,8 +4705,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4749,7 +4754,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45169</v>
+        <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4778,13 +4783,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45275</v>
+        <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4858,11 +4858,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44602</v>
+        <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4934,13 +4934,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4983,7 +4978,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4993,14 +4988,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45121</v>
+        <v>46128</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5012,13 +5007,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5061,7 +5051,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44540</v>
+        <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5091,7 +5081,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5134,7 +5124,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5148,10 +5138,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44910</v>
+        <v>45989</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5163,13 +5153,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5212,7 +5197,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5222,14 +5207,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45275</v>
+        <v>44974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5241,13 +5226,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5290,7 +5270,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5304,10 +5284,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45229</v>
+        <v>45233</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5321,11 +5301,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5368,7 +5348,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5382,10 +5362,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45229</v>
+        <v>45235</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5397,8 +5377,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5441,7 +5426,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5455,10 +5440,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45235</v>
+        <v>45756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5470,13 +5455,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5519,7 +5499,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5533,10 +5513,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>45243</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5548,8 +5528,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5592,7 +5577,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5606,10 +5591,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45989</v>
+        <v>45274</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5621,8 +5606,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5665,7 +5655,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5675,14 +5665,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45044</v>
+        <v>45050</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5696,11 +5686,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5743,7 +5733,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5757,10 +5747,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45274</v>
+        <v>45044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5774,11 +5764,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5821,7 +5811,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5835,10 +5825,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44713</v>
+        <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5850,13 +5840,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5899,7 +5884,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5909,14 +5894,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45173</v>
+        <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5928,8 +5913,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5972,7 +5962,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5986,10 +5976,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46171</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6001,13 +5991,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6050,7 +6035,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6064,10 +6049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45054</v>
+        <v>44730</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6080,7 +6065,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6123,7 +6108,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6137,10 +6122,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45243</v>
+        <v>44540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6152,13 +6137,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6201,7 +6181,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6215,10 +6195,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45874</v>
+        <v>44973</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6231,7 +6211,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>10.6</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6274,7 +6254,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6288,10 +6268,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45215</v>
+        <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6303,8 +6283,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6347,7 +6332,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6361,10 +6346,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44730</v>
+        <v>46171</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6376,8 +6361,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6420,7 +6410,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6434,10 +6424,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44602</v>
+        <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6449,13 +6439,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>10.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6498,7 +6483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6512,10 +6497,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44872</v>
+        <v>45054</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6528,7 +6513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6571,7 +6556,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6585,10 +6570,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44725</v>
+        <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6601,7 +6586,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6644,7 +6629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6658,10 +6643,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45309</v>
+        <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6673,8 +6658,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6717,7 +6707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6727,14 +6717,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44973</v>
+        <v>45275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6746,8 +6736,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6790,7 +6785,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19217-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,10 +6799,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46132</v>
+        <v>46227</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6819,13 +6814,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6868,7 +6858,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6882,10 +6872,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46128</v>
+        <v>46227</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6898,7 +6888,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6941,7 +6931,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6955,10 +6945,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44841</v>
+        <v>46273</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6970,13 +6960,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7019,7 +7004,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7033,10 +7018,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44630</v>
+        <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7049,7 +7034,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7092,7 +7077,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7106,10 +7091,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7122,7 +7107,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7165,7 +7150,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7179,10 +7164,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>44875</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7194,8 +7179,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7238,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7252,10 +7242,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46227</v>
+        <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7268,7 +7258,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7311,7 +7301,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7328,7 +7318,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7341,7 +7331,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7401,7 +7391,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7457,7 +7447,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7467,14 +7457,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7487,7 +7477,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7547,7 +7537,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7620,7 +7610,7 @@
         <v>46274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7676,7 +7666,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7690,10 +7680,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46273</v>
+        <v>45309</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7706,7 +7696,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7749,7 +7739,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7759,14 +7749,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>45792</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7778,8 +7768,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7822,7 +7817,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7895,24 +7890,24 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>S 1582-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46254</v>
+        <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7925,7 +7920,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7965,10 +7960,10 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="15" customHeight="1">
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S 1582-2024</t>
+          <t>S 710-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7982,10 +7977,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45427</v>
+        <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7997,8 +7992,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8037,84 +8037,6 @@
         <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>S 710-2025</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>45720</v>
-      </c>
-      <c r="E90" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45372</v>
+        <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1571,51 +1571,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
@@ -1639,7 +1643,7 @@
         <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1731,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1737,14 +1741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45084</v>
+        <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1757,20 +1761,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1781,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1793,50 +1797,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46107</v>
+        <v>45541</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1865,13 +1865,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,46 +1902,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1960,10 +1959,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45989</v>
+        <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1976,16 +1975,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2000,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2012,46 +2011,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2065,10 +2064,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45541</v>
+        <v>45791</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,8 +2079,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2117,50 +2121,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45167</v>
+        <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,11 +2189,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2202,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2214,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2230,42 +2235,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2279,10 +2284,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>45372</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,26 +2299,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2324,58 +2324,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46171</v>
+        <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,11 +2406,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2450,42 +2450,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44610</v>
+        <v>45989</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,17 +2515,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2555,42 +2555,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44630</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2656,46 +2656,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45791</v>
+        <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2726,11 +2726,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2770,35 +2770,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44531-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44840</v>
+        <v>44725</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44725</v>
+        <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44610</v>
+        <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 44531-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44523</v>
+        <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44872</v>
+        <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45309</v>
+        <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,8 +4169,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4213,7 +4218,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4227,10 +4232,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44841</v>
+        <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,13 +4247,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4291,7 +4291,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45229</v>
+        <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4320,13 +4320,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4369,7 +4364,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4379,14 +4374,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44602</v>
+        <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4400,11 +4395,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4447,7 +4442,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4457,14 +4452,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45884</v>
+        <v>44875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4476,8 +4471,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45121</v>
+        <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44910</v>
+        <v>44841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4629,11 +4629,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44834</v>
+        <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4705,13 +4705,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4771,7 +4766,7 @@
         <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4827,7 +4822,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4837,14 +4832,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45169</v>
+        <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4856,13 +4851,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4905,7 +4895,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4919,10 +4909,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45173</v>
+        <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4934,8 +4924,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4978,7 +4973,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4988,14 +4983,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46128</v>
+        <v>45275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5007,8 +5002,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44725</v>
+        <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5080,8 +5080,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5124,7 +5129,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5138,10 +5143,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45989</v>
+        <v>44540</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5154,7 +5159,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5197,7 +5202,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5207,14 +5212,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44974</v>
+        <v>45121</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5226,8 +5231,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5270,7 +5280,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5284,10 +5294,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45233</v>
+        <v>44910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5301,11 +5311,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5348,7 +5358,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5362,10 +5372,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45235</v>
+        <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5377,13 +5387,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5426,7 +5431,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5436,14 +5441,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45756</v>
+        <v>45275</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5455,8 +5460,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5499,7 +5509,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5513,10 +5523,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45243</v>
+        <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5530,11 +5540,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5577,7 +5587,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5591,10 +5601,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45274</v>
+        <v>45229</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5608,11 +5618,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5655,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5665,14 +5675,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45050</v>
+        <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5684,13 +5694,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5733,7 +5738,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5747,10 +5752,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45044</v>
+        <v>45235</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5764,11 +5769,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5811,7 +5816,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45215</v>
+        <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5841,7 +5846,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5884,7 +5889,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5894,14 +5899,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45275</v>
+        <v>45044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5915,11 +5920,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5962,7 +5967,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5976,10 +5981,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5991,8 +5996,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6035,7 +6045,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6049,10 +6059,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44730</v>
+        <v>45274</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6064,8 +6074,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6108,7 +6123,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6122,10 +6137,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44540</v>
+        <v>45173</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6138,7 +6153,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6181,7 +6196,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6195,10 +6210,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44973</v>
+        <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6211,7 +6226,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6254,7 +6269,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6268,10 +6283,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44713</v>
+        <v>45243</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,11 +6300,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6332,7 +6347,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6346,10 +6361,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46171</v>
+        <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6361,13 +6376,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6420,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6434,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45874</v>
+        <v>45989</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6440,7 +6450,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.6</v>
+        <v>4.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6493,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6497,10 +6507,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45054</v>
+        <v>44730</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6523,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6566,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,10 +6580,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45229</v>
+        <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6586,7 +6596,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6646,7 +6656,7 @@
         <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6707,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6717,14 +6727,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45275</v>
+        <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6736,13 +6746,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6785,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6799,10 +6804,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46227</v>
+        <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6815,7 +6820,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6858,7 +6863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6872,10 +6877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46227</v>
+        <v>46171</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6887,8 +6892,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>9.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6931,7 +6941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6945,10 +6955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46273</v>
+        <v>45874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6961,7 +6971,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7021,7 +7031,7 @@
         <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7091,10 +7101,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7107,7 +7117,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7150,7 +7160,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7164,10 +7174,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44875</v>
+        <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7179,13 +7189,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7233,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7245,7 +7250,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7258,7 +7263,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7301,7 +7306,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7311,14 +7316,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7331,7 +7336,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7374,7 +7379,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7384,14 +7389,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7404,7 +7409,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7447,7 +7452,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7457,14 +7462,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7477,7 +7482,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7520,7 +7525,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7537,7 +7542,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7550,7 +7555,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7593,7 +7598,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7607,10 +7612,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7623,7 +7628,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7666,7 +7671,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7676,14 +7681,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7696,7 +7701,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7739,7 +7744,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7753,10 +7758,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45792</v>
+        <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7768,13 +7773,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45541</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45791</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45372</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45989</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44725</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>45275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44540</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45121</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45275</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45229</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45235</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45274</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45173</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45243</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45989</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44730</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>46171</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45084</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45426</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45541</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45791</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45372</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45989</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46171</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44725</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44523</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45309</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44841</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>45275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44540</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45121</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45275</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45229</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45235</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45274</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45173</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45054</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45243</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45989</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44730</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>46171</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>46227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>46227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46274</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46274</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>46274</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46274</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 19216-2026</t>
+          <t>A 37238-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46132</v>
+        <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1329,22 +1329,17 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1359,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1375,149 +1370,154 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Skogsknipprot
+Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37238-2026 artfynd.xlsx", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37238-2026 karta.png", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37238-2026 georefererad karta.tif", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37238-2026 FSC-klagomål.docx", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37238-2026 FSC-klagomål mail.docx", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37238-2026 tillsynsbegäran.docx", "A 37238-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37238-2026 tillsynsbegäran mail.docx", "A 37238-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 19216-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Motaggsvamp
 Tallticka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 19216-2026 artfynd.xlsx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 19216-2026 karta.png", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 19216-2026 georefererad karta.tif", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 19216-2026 FSC-klagomål.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 19216-2026 FSC-klagomål mail.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 19216-2026 tillsynsbegäran.docx", "A 19216-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 19216-2026 tillsynsbegäran mail.docx", "A 19216-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 37238-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37238-2026 artfynd.xlsx", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37238-2026 karta.png", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37238-2026 georefererad karta.tif", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37238-2026 FSC-klagomål.docx", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37238-2026 FSC-klagomål mail.docx", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37238-2026 tillsynsbegäran.docx", "A 37238-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37238-2026 tillsynsbegäran mail.docx", "A 37238-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45084</v>
+        <v>44630</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1583,50 +1583,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1640,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45426</v>
+        <v>46171</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1655,11 +1651,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1668,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1680,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1692,46 +1693,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1745,10 +1746,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45167</v>
+        <v>45791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1760,11 +1761,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1773,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1785,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1797,46 +1803,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1850,10 +1856,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45541</v>
+        <v>45989</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1866,17 +1872,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1902,50 +1908,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 41251-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1959,10 +1961,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44630</v>
+        <v>46300</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1974,14 +1976,19 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2011,46 +2018,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2064,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45791</v>
+        <v>46107</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2085,7 +2092,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>12.9</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2125,42 +2132,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2174,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44602</v>
+        <v>45372</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,26 +2196,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2219,58 +2221,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2284,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45372</v>
+        <v>45426</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2300,7 +2302,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2333,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2344,38 +2346,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2385,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46107</v>
+        <v>45084</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,13 +2406,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>12.9</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2450,42 +2447,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2499,10 +2500,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45989</v>
+        <v>45541</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,16 +2516,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2539,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2551,46 +2552,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44610</v>
+        <v>45167</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2620,20 +2625,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2644,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,46 +2661,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2709,10 +2714,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46171</v>
+        <v>44602</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2735,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2766,46 +2771,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41251-2026</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46300</v>
+        <v>44610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2834,13 +2839,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2884,31 +2884,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24281-2022</t>
+          <t>A 44531-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44725</v>
+        <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8295-2022</t>
+          <t>A 24281-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44610</v>
+        <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3770,7 +3770,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 67220-2021</t>
+          <t>A 8295-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44523</v>
+        <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44531-2022</t>
+          <t>A 67220-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44840</v>
+        <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44713</v>
+        <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.1</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45309</v>
+        <v>44713</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,8 +4096,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4140,7 +4145,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4150,14 +4155,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45233</v>
+        <v>45275</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4175,7 +4180,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4218,7 +4223,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7926-2023</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4228,14 +4233,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44973</v>
+        <v>45884</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4248,7 +4253,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4291,7 +4296,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50031-2023</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4305,10 +4310,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45215</v>
+        <v>46171</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4320,8 +4325,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4364,7 +4374,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19487-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4374,14 +4384,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45050</v>
+        <v>45874</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4393,13 +4403,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4442,7 +4447,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 52878-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4456,10 +4461,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44875</v>
+        <v>44872</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4471,13 +4476,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44834</v>
+        <v>44875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 2177-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44841</v>
+        <v>45309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4627,13 +4627,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4676,7 +4671,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44974</v>
+        <v>45792</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4705,8 +4700,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44630</v>
+        <v>45989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4822,7 +4822,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4832,14 +4832,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45884</v>
+        <v>46227</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4895,7 +4895,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45169</v>
+        <v>46227</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4924,13 +4924,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4973,7 +4968,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63586-2023</t>
+          <t>A 36919-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4983,14 +4978,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45275</v>
+        <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5002,13 +4997,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5051,7 +5041,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5065,10 +5055,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44602</v>
+        <v>46227</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5080,13 +5070,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5129,7 +5114,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 71540-2021</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5143,10 +5128,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44540</v>
+        <v>46274</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5159,7 +5144,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5202,7 +5187,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5212,14 +5197,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45121</v>
+        <v>46274</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5231,13 +5216,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5280,7 +5260,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 37305-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5294,10 +5274,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44910</v>
+        <v>46274</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5309,13 +5289,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5358,7 +5333,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5368,14 +5343,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45309</v>
+        <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5388,7 +5363,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5431,7 +5406,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 37266-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5445,10 +5420,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45275</v>
+        <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5460,13 +5435,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5509,7 +5479,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5523,10 +5493,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45792</v>
+        <v>46274</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5538,13 +5508,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5587,7 +5552,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5601,10 +5566,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45229</v>
+        <v>46274</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5616,13 +5581,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5665,7 +5625,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53337-2023</t>
+          <t>A 44969-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5679,10 +5639,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45229</v>
+        <v>44841</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5694,8 +5654,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5738,7 +5703,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 2172-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5752,10 +5717,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45235</v>
+        <v>45309</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5767,13 +5732,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5816,7 +5776,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 34328-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5830,10 +5790,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45756</v>
+        <v>46254</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5846,7 +5806,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5889,7 +5849,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18793-2023</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5903,10 +5863,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45044</v>
+        <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5918,13 +5878,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5967,7 +5922,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22529-2022</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5981,10 +5936,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44713</v>
+        <v>45229</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5998,11 +5953,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6045,7 +6000,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6059,10 +6014,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45274</v>
+        <v>44602</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6080,7 +6035,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6123,7 +6078,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6133,14 +6088,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45173</v>
+        <v>45121</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6152,8 +6107,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6196,7 +6156,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19903-2023</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6210,10 +6170,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45054</v>
+        <v>44910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6225,8 +6185,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6269,7 +6234,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6283,10 +6248,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45243</v>
+        <v>44834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6300,11 +6265,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6347,7 +6312,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50020-2023</t>
+          <t>A 11430-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6361,10 +6326,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45215</v>
+        <v>44630</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6377,7 +6342,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6420,7 +6385,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6434,10 +6399,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45989</v>
+        <v>45169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6449,8 +6414,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6493,7 +6463,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25278-2022</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6507,10 +6477,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44730</v>
+        <v>45173</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6523,7 +6493,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6566,7 +6536,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 24283-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6580,10 +6550,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46128</v>
+        <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6596,7 +6566,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6639,7 +6609,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6653,10 +6623,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44602</v>
+        <v>44974</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6668,13 +6638,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6717,7 +6682,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6731,10 +6696,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44872</v>
+        <v>45233</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6746,8 +6711,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6790,7 +6760,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,10 +6774,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44725</v>
+        <v>45235</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6819,8 +6789,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6863,7 +6838,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6877,10 +6852,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46171</v>
+        <v>45756</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6892,13 +6867,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6941,7 +6911,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6955,10 +6925,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45874</v>
+        <v>45243</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6970,8 +6940,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7014,7 +6989,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7028,10 +7003,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46227</v>
+        <v>45274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7043,8 +7018,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7087,7 +7067,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7097,14 +7077,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46227</v>
+        <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7116,8 +7096,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7160,7 +7145,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7174,10 +7159,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46227</v>
+        <v>45044</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7189,8 +7174,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>9.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7233,7 +7223,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7247,10 +7237,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46274</v>
+        <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7263,7 +7253,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7306,7 +7296,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7320,10 +7310,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7335,8 +7325,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7379,7 +7374,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7393,10 +7388,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46274</v>
+        <v>45215</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7409,7 +7404,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7452,7 +7447,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7466,10 +7461,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46274</v>
+        <v>44730</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7482,7 +7477,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7525,7 +7520,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7539,10 +7534,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46274</v>
+        <v>44540</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7555,7 +7550,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7598,7 +7593,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 7926-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46273</v>
+        <v>44973</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7628,7 +7623,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7671,7 +7666,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7681,14 +7676,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46274</v>
+        <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7700,8 +7695,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7744,7 +7744,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46274</v>
+        <v>45054</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46254</v>
+        <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         <v>45427</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt NYKVARN.xlsx
+++ b/Översikt NYKVARN.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>46041</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44862</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 37238-2026</t>
+          <t>A 19216-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46274</v>
+        <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1329,18 +1329,23 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1354,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1370,154 +1375,149 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Motaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 19216-2026 artfynd.xlsx", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 19216-2026 karta.png", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 19216-2026 georefererad karta.tif", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 19216-2026 FSC-klagomål.docx", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 19216-2026 FSC-klagomål mail.docx", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 19216-2026 tillsynsbegäran.docx", "A 19216-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 19216-2026 tillsynsbegäran mail.docx", "A 19216-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 37238-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Skogsknipprot
 Svart trolldruva</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37238-2026 artfynd.xlsx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37238-2026 karta.png", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37238-2026 georefererad karta.tif", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37238-2026 FSC-klagomål.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37238-2026 FSC-klagomål mail.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37238-2026 tillsynsbegäran.docx", "A 37238-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37238-2026 tillsynsbegäran mail.docx", "A 37238-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 19216-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NYKVARN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 19216-2026 artfynd.xlsx", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 19216-2026 karta.png", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 19216-2026 georefererad karta.tif", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 19216-2026 FSC-klagomål.docx", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 19216-2026 FSC-klagomål mail.docx", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 19216-2026 tillsynsbegäran.docx", "A 19216-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 19216-2026 tillsynsbegäran mail.docx", "A 19216-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11393-2022</t>
+          <t>A 18848-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44630</v>
+        <v>45426</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1547,20 +1547,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1587,42 +1587,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24790-2026</t>
+          <t>A 23279-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46171</v>
+        <v>45791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1697,42 +1697,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23279-2025</t>
+          <t>A 39539-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45791</v>
+        <v>45167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1761,26 +1761,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -1791,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1803,46 +1798,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 23279-2025 artfynd.xlsx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 23279-2025 karta.png", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 23279-2025 georefererad karta.tif", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 23279-2025 FSC-klagomål.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 23279-2025 FSC-klagomål mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 23279-2025 tillsynsbegäran.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 23279-2025 tillsynsbegäran mail.docx", "A 23279-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59342-2025</t>
+          <t>A 11393-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1856,10 +1851,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45989</v>
+        <v>44630</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1872,16 +1867,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1896,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1908,46 +1903,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11393-2022 artfynd.xlsx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11393-2022 karta.png", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11393-2022 georefererad karta.tif", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11393-2022 FSC-klagomål.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11393-2022 FSC-klagomål mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11393-2022 tillsynsbegäran.docx", "A 11393-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11393-2022 tillsynsbegäran mail.docx", "A 11393-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41251-2026</t>
+          <t>A 11388-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1961,10 +1956,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46300</v>
+        <v>45372</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1976,26 +1971,21 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -2006,58 +1996,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15912-2026</t>
+          <t>A 59342-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2061,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46107</v>
+        <v>45989</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,23 +2076,18 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2116,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2132,42 +2117,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 59342-2025 artfynd.xlsx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 59342-2025 karta.png", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 59342-2025 georefererad karta.tif", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 59342-2025 FSC-klagomål.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 59342-2025 FSC-klagomål mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 59342-2025 tillsynsbegäran.docx", "A 59342-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 59342-2025 tillsynsbegäran mail.docx", "A 59342-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11388-2024</t>
+          <t>A 15912-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45372</v>
+        <v>46107</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,11 +2181,16 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>12.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2209,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2221,58 +2211,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 11388-2024 artfynd.xlsx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 15912-2026 artfynd.xlsx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 11388-2024 karta.png", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 15912-2026 karta.png", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 11388-2024 georefererad karta.tif", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 15912-2026 georefererad karta.tif", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 11388-2024 FSC-klagomål.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 15912-2026 FSC-klagomål.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 11388-2024 FSC-klagomål mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 15912-2026 FSC-klagomål mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 11388-2024 tillsynsbegäran.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 15912-2026 tillsynsbegäran.docx", "A 15912-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 11388-2024 tillsynsbegäran mail.docx", "A 11388-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 15912-2026 tillsynsbegäran mail.docx", "A 15912-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18848-2024</t>
+          <t>A 25754-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2282,14 +2272,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45426</v>
+        <v>45084</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2302,10 +2292,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2314,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2326,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2338,46 +2328,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 18848-2024 artfynd.xlsx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 18848-2024 karta.png", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 18848-2024 georefererad karta.tif", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 18848-2024 FSC-klagomål.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 18848-2024 FSC-klagomål mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 18848-2024 tillsynsbegäran.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 18848-2024 tillsynsbegäran mail.docx", "A 18848-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 25754-2023</t>
+          <t>A 6876-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2381,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45084</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,8 +2400,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2443,50 +2442,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 25754-2023 artfynd.xlsx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 25754-2023 karta.png", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 25754-2023 georefererad karta.tif", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 25754-2023 FSC-klagomål.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 25754-2023 FSC-klagomål mail.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 25754-2023 tillsynsbegäran.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 25754-2023 tillsynsbegäran mail.docx", "A 25754-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 25754-2023 prioriterade fågelarter.docx", "A 25754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37597-2024</t>
+          <t>A 24790-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2500,10 +2495,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45541</v>
+        <v>46171</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,8 +2510,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2552,50 +2552,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 24790-2026 artfynd.xlsx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 24790-2026 karta.png", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 24790-2026 georefererad karta.tif", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 24790-2026 FSC-klagomål.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 24790-2026 FSC-klagomål mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 24790-2026 tillsynsbegäran.docx", "A 24790-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 24790-2026 tillsynsbegäran mail.docx", "A 24790-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39539-2023</t>
+          <t>A 8285-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2609,10 +2605,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45167</v>
+        <v>44610</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2625,10 +2621,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2637,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2649,10 +2645,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2661,46 +2657,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 39539-2023 artfynd.xlsx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 39539-2023 karta.png", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 39539-2023 georefererad karta.tif", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 39539-2023 FSC-klagomål.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 39539-2023 FSC-klagomål mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 39539-2023 tillsynsbegäran.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 39539-2023 tillsynsbegäran mail.docx", "A 39539-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6876-2022</t>
+          <t>A 37597-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2714,10 +2710,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44602</v>
+        <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2729,13 +2725,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2775,42 +2766,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 6876-2022 artfynd.xlsx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 37597-2024 artfynd.xlsx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 6876-2022 karta.png", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 37597-2024 karta.png", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 6876-2022 georefererad karta.tif", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 37597-2024 georefererad karta.tif", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 6876-2022 FSC-klagomål.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 37597-2024 FSC-klagomål.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 6876-2022 FSC-klagomål mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 37597-2024 FSC-klagomål mail.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 6876-2022 tillsynsbegäran.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 37597-2024 tillsynsbegäran.docx", "A 37597-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 6876-2022 tillsynsbegäran mail.docx", "A 6876-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 37597-2024 tillsynsbegäran mail.docx", "A 37597-2024")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/fåglar/A 37597-2024 prioriterade fågelarter.docx", "A 37597-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8285-2022</t>
+          <t>A 41251-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44610</v>
+        <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2839,8 +2834,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2884,31 +2884,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 8285-2022 artfynd.xlsx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/artfynd/A 41251-2026 artfynd.xlsx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 8285-2022 karta.png", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor/A 41251-2026 karta.png", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 8285-2022 georefererad karta.tif", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/kartor_geotiff/A 41251-2026 georefererad karta.tif", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 8285-2022 FSC-klagomål.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomål/A 41251-2026 FSC-klagomål.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 8285-2022 FSC-klagomål mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/klagomålsmail/A 41251-2026 FSC-klagomål mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 8285-2022 tillsynsbegäran.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsyn/A 41251-2026 tillsynsbegäran.docx", "A 41251-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 8285-2022 tillsynsbegäran mail.docx", "A 8285-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0140/tillsynsmail/A 41251-2026 tillsynsbegäran mail.docx", "A 41251-2026")</f>
         <v/>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
         <v>45055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44550</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44725</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44523</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44635</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6854-2022</t>
+          <t>A 22531-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44602</v>
+        <v>44713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22531-2022</t>
+          <t>A 43230-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44713</v>
+        <v>44834</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.1</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4145,7 +4145,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 63592-2023</t>
+          <t>A 52963-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45275</v>
+        <v>44875</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4176,11 +4176,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38535-2025</t>
+          <t>A 50031-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4233,14 +4233,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45884</v>
+        <v>45215</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24796-2026</t>
+          <t>A 23655-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46171</v>
+        <v>45792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4327,11 +4327,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36986-2025</t>
+          <t>A 19487-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45874</v>
+        <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4403,8 +4403,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>10.6</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4447,7 +4452,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52878-2022</t>
+          <t>A 8096-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4461,10 +4466,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44872</v>
+        <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4477,7 +4482,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4520,7 +4525,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52963-2022</t>
+          <t>A 38535-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4530,14 +4535,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44875</v>
+        <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4549,13 +4554,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2177-2024</t>
+          <t>A 40168-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45309</v>
+        <v>45169</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4625,6 +4625,11 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>NYKVARN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -4671,7 +4676,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23655-2025</t>
+          <t>A 6857-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4685,10 +4690,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45792</v>
+        <v>44602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4702,11 +4707,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4749,7 +4754,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59348-2025</t>
+          <t>A 71540-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4763,10 +4768,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45989</v>
+        <v>44540</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4779,7 +4784,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4822,7 +4827,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31740-2026</t>
+          <t>A 60324-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4836,10 +4841,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46227</v>
+        <v>44910</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4851,8 +4856,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4895,7 +4905,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31741-2026</t>
+          <t>A 53307-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4909,10 +4919,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46227</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4924,8 +4934,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>9.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4968,7 +4983,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36919-2026</t>
+          <t>A 53337-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4982,10 +4997,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46273</v>
+        <v>45229</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4998,7 +5013,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5041,7 +5056,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31731-2026</t>
+          <t>A 54670-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5055,10 +5070,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46227</v>
+        <v>45235</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5070,8 +5085,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5114,7 +5134,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37306-2026</t>
+          <t>A 59348-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5128,10 +5148,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46274</v>
+        <v>45989</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5144,7 +5164,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5187,7 +5207,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37271-2026</t>
+          <t>A 18793-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5201,10 +5221,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46274</v>
+        <v>45044</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5216,8 +5236,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5260,7 +5285,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37305-2026</t>
+          <t>A 22529-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5274,10 +5299,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46274</v>
+        <v>44713</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5289,8 +5314,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>8.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5333,7 +5363,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37244-2026</t>
+          <t>A 18780-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5343,14 +5373,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46274</v>
+        <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5363,7 +5393,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5406,7 +5436,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37266-2026</t>
+          <t>A 54583-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5416,14 +5446,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46274</v>
+        <v>45233</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5435,8 +5465,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5479,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37307-2026</t>
+          <t>A 63586-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5489,14 +5524,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46274</v>
+        <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5508,8 +5543,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5552,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37309-2026</t>
+          <t>A 32555-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5562,14 +5602,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46274</v>
+        <v>45121</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5581,8 +5621,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5625,7 +5670,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44969-2022</t>
+          <t>A 63592-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5635,14 +5680,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44841</v>
+        <v>45275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5656,11 +5701,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5703,7 +5748,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2172-2024</t>
+          <t>A 17328-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5717,10 +5762,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45309</v>
+        <v>45756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5733,7 +5778,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5776,7 +5821,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34328-2026</t>
+          <t>A 24796-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5790,10 +5835,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46254</v>
+        <v>46171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5805,8 +5850,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5849,7 +5899,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18780-2026</t>
+          <t>A 63400-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5863,10 +5913,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46128</v>
+        <v>45274</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5878,8 +5928,13 @@
           <t>NYKVARN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5922,7 +5977,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53307-2023</t>
+          <t>A 36986-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5936,10 +5991,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45229</v>
+        <v>45874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5951,13 +6006,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>10.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6000,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6857-2022</t>
+          <t>A 41681-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6014,10 +6064,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44602</v>
+        <v>45173</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6029,13 +6079,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6078,7 +6123,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32555-2023</t>
+          <t>A 19903-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6088,14 +6133,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45121</v>
+        <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6107,13 +6152,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6156,7 +6196,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60324-2022</t>
+          <t>A 56639-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6170,10 +6210,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44910</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6187,11 +6227,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6234,7 +6274,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43230-2022</t>
+          <t>A 50020-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6248,10 +6288,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44834</v>
+        <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6263,13 +6303,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6312,7 +6347,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11430-2022</t>
+          <t>A 25278-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6326,10 +6361,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44630</v>
+        <v>44730</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6342,7 +6377,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6385,7 +6420,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40168-2023</t>
+          <t>A 6854-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6399,10 +6434,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45169</v>
+        <v>44602</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6416,11 +6451,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6463,7 +6498,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41681-2023</t>
+          <t>A 31731-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6477,10 +6512,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45173</v>
+        <v>46227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6493,7 +6528,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6536,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24283-2022</t>
+          <t>A 31740-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6550,10 +6585,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44725</v>
+        <v>46227</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6566,7 +6601,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6609,7 +6644,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8096-2023</t>
+          <t>A 31741-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6623,10 +6658,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44974</v>
+        <v>46227</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6639,7 +6674,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6682,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54583-2023</t>
+          <t>A 37306-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6696,10 +6731,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45233</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6711,13 +6746,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6760,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54670-2023</t>
+          <t>A 37244-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6770,14 +6800,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45235</v>
+        <v>46274</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6789,13 +6819,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6838,7 +6863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17328-2025</t>
+          <t>A 37271-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6852,10 +6877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45756</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6868,7 +6893,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6911,7 +6936,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56639-2023</t>
+          <t>A 37307-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6925,10 +6950,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45243</v>
+        <v>46274</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6940,13 +6965,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6989,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 63400-2023</t>
+          <t>A 37309-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7003,10 +7023,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45274</v>
+        <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7018,13 +7038,8 @@
           <t>NYKVARN</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
   